--- a/mp_levantamento/levantamento_parametrico.xlsx
+++ b/mp_levantamento/levantamento_parametrico.xlsx
@@ -34,7 +34,7 @@
     <sheet name="22_SN_CAMPO_DO_RODAO" sheetId="24" state="visible" r:id="rId26"/>
     <sheet name="23_TJBA_0001568-38.2011" sheetId="25" state="visible" r:id="rId27"/>
     <sheet name="24_TJBA_8007670-17.2023" sheetId="26" state="visible" r:id="rId28"/>
-    <sheet name="25_TJBA_8008589-69.2024" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="25_TJBA_0000917-10.2015" sheetId="27" state="visible" r:id="rId29"/>
     <sheet name="DEMANDAS-TIPO" sheetId="28" state="visible" r:id="rId30"/>
     <sheet name="FONTES" sheetId="29" state="visible" r:id="rId31"/>
   </sheets>
@@ -48,12 +48,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6104" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5789" uniqueCount="958">
   <si>
     <t xml:space="preserve">Levantamento paramétrico - demandas de MP, Justiça e TCM (SEINFRA Ilhéus)</t>
   </si>
   <si>
-    <t xml:space="preserve">PROVISORIO - aguarda aprovacao</t>
+    <t xml:space="preserve">Parâmetros e triagem APROVADO em 13/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Estimativa preliminar paramétrica, não vinculante, para planejamento orçamentário. Preços SINAPI-BA 08/2026, não desonerado. Data: 13/10/2026. Levantamentos MP (pacote de 12/10) e Justiça (pacote de 13/10), sem dupla contagem.</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">JUSTICA_0006323-71.2012.8.05.0103</t>
   </si>
   <si>
-    <t xml:space="preserve">Requalificação do Estádio Municipal Mário Pessoa (Cidade Nova) – TAC</t>
+    <t xml:space="preserve">Adequação do Estádio Municipal Mário Pessoa às normas de segurança (TAC de 2012, Cidade Nova)</t>
   </si>
   <si>
     <t xml:space="preserve">Justiça</t>
   </si>
   <si>
-    <t xml:space="preserve">demanda-tipo (itens do TAC)</t>
+    <t xml:space="preserve">demanda-tipo (itens de segurança do TAC)</t>
   </si>
   <si>
     <t xml:space="preserve">17_TJBA_0006323-71.2012</t>
@@ -404,13 +404,19 @@
     <t xml:space="preserve">24_TJBA_8007670-17.2023</t>
   </si>
   <si>
-    <t xml:space="preserve">JUSTICA_8008589-69.2024.8.05.0103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidade de Acolhimento Renascer: projeto de incêndio e reforma (Conquista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25_TJBA_8008589-69.2024</t>
+    <t xml:space="preserve">JUSTICA_0000917-10.2015.5.05.0493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cercamento de toda a poligonal do antigo lixão de Itariri (ACP do MPT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">saneamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">demanda-tipo (perímetro da poligonal a medir)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25_TJBA_0000917-10.2015</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL GERAL</t>
@@ -431,15 +437,9 @@
     <t xml:space="preserve">Objetos "orçamento paramétrico" da Justiça já calculados no MP (não somados de novo; valor da aba do MP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Requalificação do Estádio Municipal Mário Pessoa (Cidade Nova) – TAC de 2012</t>
-  </si>
-  <si>
     <t xml:space="preserve">no MP: JUSTICA_0006323-71.2012.8.05.0103</t>
   </si>
   <si>
-    <t xml:space="preserve">Abrigos de ônibus na Rodovia Jorge Amado (BR-415), perto do IFBA</t>
-  </si>
-  <si>
     <t xml:space="preserve">no MP: JUSTICA_8005837-61.2023.8.05.0103</t>
   </si>
   <si>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">Quantidades: metragem do documento quando existe; nos demais casos, demanda-tipo com premissas na aba de cada objeto (a confirmar em campo/projeto).</t>
   </si>
   <si>
-    <t xml:space="preserve">BDI, contingência e fator regional: aba PARAMETROS (PROVISORIO - aguarda aprovacao).</t>
+    <t xml:space="preserve">BDI, contingência e fator regional: aba PARAMETROS (APROVADO em 13/10/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Origem "outro" = processo interno "Resposta Ministério Público" sem indicação do ramo do MP (somado em MP).</t>
   </si>
   <si>
-    <t xml:space="preserve">Justiça: só os objetos "orçamento paramétrico" do pacote da Justiça que não estavam calculados no MP (triagem_provisoria_justica.json). A triagem do MP não foi alterada.</t>
+    <t xml:space="preserve">Justiça: só os objetos "orçamento paramétrico" do pacote da Justiça que não estavam calculados no MP (triagem_provisoria_justica.json, aprovada). Retirados por decisão do usuário: reforma do Renascer e Canal do Malhado (licitação própria) e projeto de incêndio da Casa Lar Masculina (tratados à parte).</t>
   </si>
   <si>
     <t xml:space="preserve">Não usar como orçamento de licitação. Estimativa não vinculante, com SINAPI como base oficial de referência, nos termos da Lei n. 14.133/2021 e do Decreto Municipal n. 269/2025.</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">Parâmetros da estimativa (BDI, contingência e fator regional)</t>
   </si>
   <si>
-    <t xml:space="preserve">Custo = Σ(Quantidade × Preço unitário) × (1 + BDI) × (1 + Contingência) × Fator regional. Células amarelas: valores a aprovar.</t>
+    <t xml:space="preserve">Custo = Σ(Quantidade × Preço unitário) × (1 + BDI) × (1 + Contingência) × Fator regional. Células amarelas: valores aprovados em 13/10/2026 (podem ser alterados; a planilha recalcula).</t>
   </si>
   <si>
     <t xml:space="preserve">Parâmetro</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">Fonte / justificativa</t>
   </si>
   <si>
-    <t xml:space="preserve">BDI - edificações, encostas, quadras e outros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acórdão n. 2.622/2013-TCU-Plenário, "construção de edifícios": 1º quartil / médio / 3º quartil (sem CPRB; regime não desonerado).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDI - pavimentação e drenagem de vias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acórdão n. 2.622/2013-TCU-Plenário, "construção de rodovias e ferrovias": 1º quartil / médio / 3º quartil (sem CPRB).</t>
+    <t xml:space="preserve">BDI - edificações, encostas, quadras, cercamento e outros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão n. 2.622/2013-TCU-Plenário, "construção de edifícios": valor médio, único nos três cenários (sem CPRB; regime não desonerado).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDI - pavimentação, drenagem e infraestrutura de vias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acórdão n. 2.622/2013-TCU-Plenário, "construção de rodovias e ferrovias": valor médio, único nos três cenários (sem CPRB).</t>
   </si>
   <si>
     <t xml:space="preserve">Contingência (projeto, sondagem, topografia, licenciamento, fiscalização)</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">Fator regional</t>
   </si>
   <si>
-    <t xml:space="preserve">SINAPI coleta preços na capital (Salvador). Máximo cobre frete até Ilhéus, acesso difícil e mobilização (parâmetro declarado).</t>
+    <t xml:space="preserve">1,00 nos três cenários: SINAPI-BA, localidade Salvador, regime não desonerado, adotado como referência de preço para Ilhéus (decisão de 13/10/2026).</t>
   </si>
   <si>
     <t xml:space="preserve">Preços unitários: SINAPI/CAIXA, ref. 08/2026, Bahia (localidade Salvador), regime não desonerado; encargos sociais horista 117,73% e mensalista 72,85%.</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">TOTAL ESTIMADO (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimativa preliminar paramétrica, não vinculante, para planejamento orçamentário. Não substitui o orçamento detalhado do projeto. PROVISORIO - aguarda aprovacao</t>
+    <t xml:space="preserve">Estimativa preliminar paramétrica, não vinculante, para planejamento orçamentário. Não substitui o orçamento detalhado do projeto. Parâmetros APROVADO em 13/10/2026.</t>
   </si>
   <si>
     <t xml:space="preserve">02 - Conclusão de unidades escolares paralisadas (Recomendação MPBA 02/2025)</t>
@@ -2279,22 +2279,25 @@
     <t xml:space="preserve">extintor</t>
   </si>
   <si>
-    <t xml:space="preserve">17 - Requalificação do Estádio Municipal Mário Pessoa (Cidade Nova) – TAC</t>
+    <t xml:space="preserve">17 - Adequação do Estádio Municipal Mário Pessoa às normas de segurança (TAC de 2012, Cidade Nova)</t>
   </si>
   <si>
     <t xml:space="preserve">Estádio Municipal Mário Pessoa, Praça Guadalajara, s/nº, Cidade Nova</t>
   </si>
   <si>
-    <t xml:space="preserve">Itens do TAC de 2012: extintores, guarda-corpos, sinalização de saídas, casas de força, alarme e SPDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantidades-tipo para estádio de pequeno porte (premissa; o relatório técnico pedido pela PGM deve confirmar).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Central de alarme e acionadores não têm preço no SINAPI-BA usado e não estão incluídos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Segurança contra incêndio e pânico</t>
+    <t xml:space="preserve">Escopo estrito, por decisão do usuário (13/10/2026): só a adequação às normas de segurança previstas no TAC de 2012 (extintores, guarda-corpos, sinalização e saídas de emergência, casas de força e SPDA). Sem reforma geral, pintura ou acessibilidade.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantidades-tipo para estádio de pequeno porte (premissa); o relatório técnico e o projeto de segurança contra incêndio e pânico devem confirmá-las.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Central de alarme, acionadores e sirenes não têm preço no SINAPI-BA usado e não estão incluídos. Brigada de incêndio (treinamento) e projeto de segurança contra incêndio estão na contingência.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se o projeto aprovado pelo Corpo de Bombeiros exigir sistema de hidrantes, o custo será acrescido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Extintores</t>
   </si>
   <si>
     <t xml:space="preserve">101911</t>
@@ -2303,7 +2306,31 @@
     <t xml:space="preserve">EXTINTOR DE INCÊNDIO PORTÁTIL COM CARGA DE PQS DE 12 KG, CLASSE BC - FORNECIMENTO E INSTALAÇÃO. AF_01/2026_PE</t>
   </si>
   <si>
-    <t xml:space="preserve">extintores PQS 12 kg</t>
+    <t xml:space="preserve">extintores PQS 12 kg nas arquibancadas e circulações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTINTOR DE INCÊNDIO PORTÁTIL COM CARGA DE ÁGUA PRESSURIZADA DE 10 L, CLASSE A - FORNECIMENTO E INSTALAÇÃO. AF_01/2026_PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extintores de água pressurizada 10 L (classe A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTINTOR DE INCÊNDIO PORTÁTIL COM CARGA DE CO2 DE 6 KG, CLASSE BC - FORNECIMENTO E INSTALAÇÃO. AF_01/2026_PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">extintores de CO2 6 kg nas casas de força</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Iluminação e sinalização de emergência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">luminárias de emergência nas rotas de fuga</t>
   </si>
   <si>
     <t xml:space="preserve">37558</t>
@@ -2312,10 +2339,34 @@
     <t xml:space="preserve">PLACA DE SINALIZACAO DE SEGURANCA CONTRA INCENDIO, FOTOLUMINESCENTE, RETANGULAR, *20 X 40* CM, EM PVC *2* MM ANTI-CHAMAS (SIMBOLOS, CORES E PICTOGRAMAS CONFORME NBR 16820)</t>
   </si>
   <si>
-    <t xml:space="preserve">placas de saída de emergência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Guarda-corpos</t>
+    <t xml:space="preserve">placas fotoluminescentes de saída de emergência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACA DE SINALIZACAO DE SEGURANCA CONTRA INCENDIO - ALERTA, TRIANGULAR, BASE DE *30* CM, EM PVC *2* MM ANTI-CHAMAS (SIMBOLOS, CORES E PICTOGRAMAS CONFORME NBR 16820)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">placas de alerta (risco elétrico, extintores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Saídas de emergência</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA ANTIPANICO DUPLA, CEGA EM LADO OPOSTO, COR CINZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barras antipânico duplas nos portões de saída (insumo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Guarda-corpos</t>
   </si>
   <si>
     <t xml:space="preserve">99844</t>
@@ -2324,10 +2375,10 @@
     <t xml:space="preserve">GUARDA-CORPO DE AÇO GALVANIZADO DE 1,10M, MONTANTES TUBULARES DE 1.1/2" ESPAÇADOS 1,20M, TRAVESSA SUPERIOR DE 2", GRADIL FORMADO POR BARRAS CHATAS DE 32X4,8MM, FIXADO COM ADESIVO ESTRUTURAL EPOXI. AF_10/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">guarda-corpo de aço galvanizado 1,10 m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. SPDA</t>
+    <t xml:space="preserve">guarda-corpo de aço galvanizado 1,10 m em arquibancadas e desníveis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. SPDA</t>
   </si>
   <si>
     <t xml:space="preserve">96989</t>
@@ -2345,49 +2396,40 @@
     <t xml:space="preserve">CORDOALHA DE COBRE NU 50 MM², NÃO ENTERRADA, COM ISOLADOR - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
   </si>
   <si>
-    <t xml:space="preserve">cordoalha de cobre nu 50 mm²</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Arquibancadas e acessibilidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pintura das arquibancadas e muros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">105004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAMPA DE ACESSIBILIDADE EM CONCRETO MOLDADO IN LOCO, EM CALÇADA NOVA COM LARGURA MENOR À 3,00 M, FCK 25MPA, COM PISO PODOTÁTIL. AF_03/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rampas de acessibilidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 1. Serviços preliminares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 2. Demolições e retiradas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 3. Cobertura e forro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 4. Revestimentos e pisos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 5. Pintura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 6. Esquadrias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 7. Instalações</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 8. Prevenção contra incêndio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Casas de força, vestiários e áreas cobertas - 9. Entulho</t>
+    <t xml:space="preserve">cordoalha de cobre nu 50 mm² (captação e descidas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HASTE DE ATERRAMENTO, DIÂMETRO 3/4", COM 3 METROS - FORNECIMENTO E INSTALAÇÃO. AF_08/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hastes de aterramento 3/4" x 3 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIXA DE INSPEÇÃO PARA ATERRAMENTO, CIRCULAR, EM POLIETILENO, DIÂMETRO INTERNO = 0,3 M. AF_12/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">caixas de inspeção do aterramento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. Casas de força (segurança elétrica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quadros de distribuição novos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISPOSITIVO DR, 4 POLOS, SENSIBILIDADE DE 30 MA, CORRENTE DE 63 A, TIPO AC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dispositivo DR 4 polos 30 mA por quadro (insumo)</t>
   </si>
   <si>
     <t xml:space="preserve">18 - Drenagem pluvial e alagamentos nas Ruas Castro Alves e Barão do Rio Branco (Pontal)</t>
@@ -2666,31 +2708,61 @@
     <t xml:space="preserve">Recuperação do pavimento da ladeira não está incluída.</t>
   </si>
   <si>
-    <t xml:space="preserve">25 - Unidade de Acolhimento Renascer: projeto de incêndio e reforma (Conquista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unidade de Acolhimento Renascer, Av. Princesa Isabel, nº 1554, bairro Conquista</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acordo homologado: reforma da Unidade de Acolhimento Renascer, projeto de segurança contra incêndio, saída de emergência e armários.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Imóvel de 200/300/450 m² (premissa); 1/1/2 portas corta-fogo na rota de saída.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projeto de segurança contra incêndio na contingência (projetos). Armários de alvenaria não estão incluídos.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PORTA CORTA-FOGO 90X210X5CM - FORNECIMENTO E INSTALAÇÃO. AF_10/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">porta corta-fogo 90x210 na rota de saída de emergência</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demandas-tipo (premissas a aprovar uma vez por engenheiro revisor)</t>
+    <t xml:space="preserve">25 - Cercamento de toda a poligonal do antigo lixão de Itariri (ACP do MPT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antigo lixão (aterro) de Itariri, Ilhéus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentença da ACP do MPT (1ª Vara do Trabalho de Ilhéus): cercar toda a poligonal do antigo aterro de Itariri. Só o cercamento; vigilância 24 h e ações sociais cabem a outras secretarias.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perímetro de 1.500/2.500/3.500 m (premissa): a poligonal não consta do acervo e a base cartográfica aberta não pôde ser acessada. Custo linear: recalcular com o perímetro medido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambrado de 2 m com tela de arame galvanizado, mourões e mureta de concreto, com concertina no topo; 1/2/3 portões de 4,0 x 2,2 m; placas de advertência a cada 100 m.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não inclui recuperação de cerca existente, terraplenagem de taludes, drenagem nem guarita (a vigilância é da Secretaria de Ordem Pública).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">limpeza da faixa de 3 m ao longo do perímetro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Cercamento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alambrado com mourões de concreto, tela de arame galvanizado e mureta de concreto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INSTALAÇÃO DE CONCERTINA SIMPLES, ESPIRAL DE 300 MM. AF_03/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">concertina simples de 300 mm no topo do alambrado (impede a escalada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Portões de controle de acesso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portões em gradil de aço, 4,0 m x 2,2 m cada (1/2/3 portões nos cenários mín/prov/máx)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Sinalização</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLACA DE SINALIZACAO EM CHAPA DE ACO NUM 16 COM PINTURA REFLETIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">placa de advertência 1,0 x 0,5 m em chapa de aço a cada 100 m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demandas-tipo (premissas aprovadas em 13/10/2026; confirmar quantidades em campo ou projeto)</t>
   </si>
   <si>
     <t xml:space="preserve">Demanda-tipo</t>
@@ -2789,10 +2861,10 @@
     <t xml:space="preserve">Tapume, estroncas de eucalipto com mão de obra, montagem de andaime fachadeiro, tela de proteção e lona na cobertura.</t>
   </si>
   <si>
-    <t xml:space="preserve">Adequação de segurança de estádio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extintores, luminárias de emergência, sinalização de saída, guarda-corpos, SPDA, pintura de arquibancadas, rampas e reforma de casas de força/vestiários.</t>
+    <t xml:space="preserve">Adequação de segurança de estádio (TAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Só itens de segurança do TAC: extintores PQS, água e CO2, luminárias e placas de emergência, barras antipânico nas saídas, guarda-corpos, SPDA (captores, cordoalha, hastes e caixas) e quadros com DR nas casas de força. Sem reforma, pintura ou acessibilidade; sem alarme (sem preço no SINAPI-BA).</t>
   </si>
   <si>
     <t xml:space="preserve">Casa térrea + parque linear</t>
@@ -2810,10 +2882,13 @@
     <t xml:space="preserve">Via urbana-tipo + rede de água PVC DN 50 (vala 0,6 x 1,0 m) + rede de esgoto PVC DN 150 (vala 0,8 x 1,5 m, PV pré-moldado a cada 60 m) + luminária LED 68-97 W com braço a cada 35 m, em poste existente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reforma de unidade de acolhimento (Justiça)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reforma predial-tipo + porta corta-fogo na rota de saída (1/1/2 unidades); projeto de segurança contra incêndio na contingência.</t>
+    <t xml:space="preserve">Cercamento de área (Justiça)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metro de perímetro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alambrado de 2 m com tela de arame galvanizado, mourões e mureta de concreto, concertina no topo, limpeza de faixa de 3 m, placas a cada 100 m e portões em gradil de aço de 4,0 x 2,2 m.</t>
   </si>
   <si>
     <t xml:space="preserve">Fontes e limitações</t>
@@ -2828,6 +2903,9 @@
     <t xml:space="preserve">IBRAOP - OT-IBR 004/2012 (precisão do orçamento de obras públicas): ±30% para estudos preliminares em edificações. Conferido em documentos que reproduzem a OT.</t>
   </si>
   <si>
+    <t xml:space="preserve">Parâmetros (BDI, contingência e fator regional) e triagens aprovados pelo usuário em 13/10/2026.</t>
+  </si>
+  <si>
     <t xml:space="preserve">CAIXA - SINAPI: metodologias e conceitos (coleta de preços nas capitais, sem frete). Conferido em reprodução pública.</t>
   </si>
   <si>
@@ -2837,7 +2915,7 @@
     <t xml:space="preserve">Quantidades: documentos dos pacotes MP_FILTRADO de 12/10/2026 (mp_objetos.json) e JUSTICA_FILTRADO de 13/10/2026 (justica_objetos.json) e demandas-tipo desta planilha.</t>
   </si>
   <si>
-    <t xml:space="preserve">Limitação: composições sem preço na BA (ex.: imprimação, pintura de ligação, exaustores, central de alarme, locação de andaime) não estão incluídas; quantidades da maioria dos objetos são premissas a confirmar.</t>
+    <t xml:space="preserve">Limitação: composições sem preço na BA (ex.: imprimação, pintura de ligação, exaustores, central de alarme, acionadores e sirenes, locação de andaime) não estão incluídas; quantidades da maioria dos objetos são premissas a confirmar.</t>
   </si>
   <si>
     <t xml:space="preserve">Limitação: OpenStreetMap e sites oficiais não puderam ser acessados neste ambiente; comprimentos de ruas não foram medidos.</t>
@@ -2889,7 +2967,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -3393,7 +3471,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3481,7 +3559,7 @@
       </c>
       <c r="H6" s="6" t="n">
         <f aca="false">'01_MPBA_001.9.102305.2021'!J62</f>
-        <v>20375.386944066</v>
+        <v>20676.767937588</v>
       </c>
       <c r="I6" s="6" t="n">
         <f aca="false">'01_MPBA_001.9.102305.2021'!K62</f>
@@ -3489,7 +3567,7 @@
       </c>
       <c r="J6" s="6" t="n">
         <f aca="false">'01_MPBA_001.9.102305.2021'!L62</f>
-        <v>554590.51998625</v>
+        <v>492557.049459788</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>20</v>
@@ -3519,7 +3597,7 @@
       </c>
       <c r="H7" s="6" t="n">
         <f aca="false">'02_MPBA_001.9.190096.2025'!J55</f>
-        <v>330852.0063156</v>
+        <v>335745.7787208</v>
       </c>
       <c r="I7" s="6" t="n">
         <f aca="false">'02_MPBA_001.9.190096.2025'!K55</f>
@@ -3527,7 +3605,7 @@
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">'02_MPBA_001.9.190096.2025'!L55</f>
-        <v>1609322.696575</v>
+        <v>1429312.63785992</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>25</v>
@@ -3557,7 +3635,7 @@
       </c>
       <c r="H8" s="6" t="n">
         <f aca="false">'03_MPBA_001.9.24192.2024'!J41</f>
-        <v>2199510.94038312</v>
+        <v>2224706.00717513</v>
       </c>
       <c r="I8" s="6" t="n">
         <f aca="false">'03_MPBA_001.9.24192.2024'!K41</f>
@@ -3565,7 +3643,7 @@
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">'03_MPBA_001.9.24192.2024'!L41</f>
-        <v>4174865.17984169</v>
+        <v>3695736.21366124</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>30</v>
@@ -3595,7 +3673,7 @@
       </c>
       <c r="H9" s="6" t="n">
         <f aca="false">'04_MPBA_001.9.250850.2021'!J38</f>
-        <v>8137.2391716</v>
+        <v>8257.6005288</v>
       </c>
       <c r="I9" s="6" t="n">
         <f aca="false">'04_MPBA_001.9.250850.2021'!K38</f>
@@ -3603,7 +3681,7 @@
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">'04_MPBA_001.9.250850.2021'!L38</f>
-        <v>16216.155965625</v>
+        <v>14402.30521107</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>34</v>
@@ -3633,7 +3711,7 @@
       </c>
       <c r="H10" s="6" t="n">
         <f aca="false">'05_MPBA_001.9.379764.2023'!J39</f>
-        <v>63307.48679892</v>
+        <v>64032.664532319</v>
       </c>
       <c r="I10" s="6" t="n">
         <f aca="false">'05_MPBA_001.9.379764.2023'!K39</f>
@@ -3641,7 +3719,7 @@
       </c>
       <c r="J10" s="6" t="n">
         <f aca="false">'05_MPBA_001.9.379764.2023'!L39</f>
-        <v>351155.122714659</v>
+        <v>310854.75763278</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>38</v>
@@ -3671,7 +3749,7 @@
       </c>
       <c r="H11" s="6" t="n">
         <f aca="false">'06_MPBA_001.9.52800.2024'!J72</f>
-        <v>638222.7754287</v>
+        <v>647662.9992966</v>
       </c>
       <c r="I11" s="6" t="n">
         <f aca="false">'06_MPBA_001.9.52800.2024'!K72</f>
@@ -3679,7 +3757,7 @@
       </c>
       <c r="J11" s="6" t="n">
         <f aca="false">'06_MPBA_001.9.52800.2024'!L72</f>
-        <v>1166732.33325</v>
+        <v>1036228.0184472</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>43</v>
@@ -3709,7 +3787,7 @@
       </c>
       <c r="H12" s="6" t="n">
         <f aca="false">'07_MPBA_003.9.153337.2023'!J53</f>
-        <v>297660.85913025</v>
+        <v>302063.6871945</v>
       </c>
       <c r="I12" s="6" t="n">
         <f aca="false">'07_MPBA_003.9.153337.2023'!K53</f>
@@ -3717,7 +3795,7 @@
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">'07_MPBA_003.9.153337.2023'!L53</f>
-        <v>2481754.0125675</v>
+        <v>2204158.54556177</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>47</v>
@@ -3747,7 +3825,7 @@
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">'08_MPBA_003.9.198543.2025'!J39</f>
-        <v>160465.94404386</v>
+        <v>162304.05728249</v>
       </c>
       <c r="I13" s="6" t="n">
         <f aca="false">'08_MPBA_003.9.198543.2025'!K39</f>
@@ -3755,7 +3833,7 @@
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">'08_MPBA_003.9.198543.2025'!L39</f>
-        <v>694200.074477024</v>
+        <v>614530.109177886</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>51</v>
@@ -3785,7 +3863,7 @@
       </c>
       <c r="H14" s="6" t="n">
         <f aca="false">'09_MPBA_003.9.476383.2022'!J52</f>
-        <v>307680.84760686</v>
+        <v>311205.285409715</v>
       </c>
       <c r="I14" s="6" t="n">
         <f aca="false">'09_MPBA_003.9.476383.2022'!K52</f>
@@ -3793,7 +3871,7 @@
       </c>
       <c r="J14" s="6" t="n">
         <f aca="false">'09_MPBA_003.9.476383.2022'!L52</f>
-        <v>1748983.4844538</v>
+        <v>1548261.15866009</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>55</v>
@@ -3823,7 +3901,7 @@
       </c>
       <c r="H15" s="6" t="n">
         <f aca="false">'10_MPF_.000105-2023'!J33</f>
-        <v>1328465.09724667</v>
+        <v>1348114.9881649</v>
       </c>
       <c r="I15" s="6" t="n">
         <f aca="false">'10_MPF_.000105-2023'!K33</f>
@@ -3831,7 +3909,7 @@
       </c>
       <c r="J15" s="6" t="n">
         <f aca="false">'10_MPF_.000105-2023'!L33</f>
-        <v>4832014.295955</v>
+        <v>4291531.53325109</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>61</v>
@@ -3861,7 +3939,7 @@
       </c>
       <c r="H16" s="6" t="n">
         <f aca="false">'11_MPF_.000183-2023'!J57</f>
-        <v>7461124.56767832</v>
+        <v>7571485.22689776</v>
       </c>
       <c r="I16" s="6" t="n">
         <f aca="false">'11_MPF_.000183-2023'!K57</f>
@@ -3869,7 +3947,7 @@
       </c>
       <c r="J16" s="6" t="n">
         <f aca="false">'11_MPF_.000183-2023'!L57</f>
-        <v>10752291.9834</v>
+        <v>9549599.25100224</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>66</v>
@@ -3899,7 +3977,7 @@
       </c>
       <c r="H17" s="6" t="n">
         <f aca="false">12_SN_MPF_FNDE_2023!J138</f>
-        <v>1290541.41567028</v>
+        <v>1309630.36132337</v>
       </c>
       <c r="I17" s="6" t="n">
         <f aca="false">12_SN_MPF_FNDE_2023!K138</f>
@@ -3907,7 +3985,7 @@
       </c>
       <c r="J17" s="6" t="n">
         <f aca="false">12_SN_MPF_FNDE_2023!L138</f>
-        <v>3763734.43457</v>
+        <v>3342743.63017955</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>70</v>
@@ -3937,7 +4015,7 @@
       </c>
       <c r="H18" s="6" t="n">
         <f aca="false">'13_MPT_000120.2022'!J52</f>
-        <v>43249.121929398</v>
+        <v>43888.838042364</v>
       </c>
       <c r="I18" s="6" t="n">
         <f aca="false">'13_MPT_000120.2022'!K52</f>
@@ -3945,7 +4023,7 @@
       </c>
       <c r="J18" s="6" t="n">
         <f aca="false">'13_MPT_000120.2022'!L52</f>
-        <v>400710.7983175</v>
+        <v>355889.474112968</v>
       </c>
       <c r="K18" s="5" t="s">
         <v>74</v>
@@ -3975,7 +4053,7 @@
       </c>
       <c r="H19" s="6" t="n">
         <f aca="false">'14_MPT_000252.2024'!J53</f>
-        <v>62764.16907915</v>
+        <v>63692.5405347</v>
       </c>
       <c r="I19" s="6" t="n">
         <f aca="false">'14_MPT_000252.2024'!K53</f>
@@ -3983,7 +4061,7 @@
       </c>
       <c r="J19" s="6" t="n">
         <f aca="false">'14_MPT_000252.2024'!L53</f>
-        <v>797089.8084325</v>
+        <v>707931.690223832</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>77</v>
@@ -4013,7 +4091,7 @@
       </c>
       <c r="H20" s="6" t="n">
         <f aca="false">'15_MPT_000282.2023'!J52</f>
-        <v>62764.16907915</v>
+        <v>63692.5405347</v>
       </c>
       <c r="I20" s="6" t="n">
         <f aca="false">'15_MPT_000282.2023'!K52</f>
@@ -4021,7 +4099,7 @@
       </c>
       <c r="J20" s="6" t="n">
         <f aca="false">'15_MPT_000282.2023'!L52</f>
-        <v>598900.303375</v>
+        <v>531910.5821684</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>80</v>
@@ -4051,7 +4129,7 @@
       </c>
       <c r="H21" s="6" t="n">
         <f aca="false">'16_MPT_000393.2023'!J34</f>
-        <v>41628.819078</v>
+        <v>42244.568604</v>
       </c>
       <c r="I21" s="6" t="n">
         <f aca="false">'16_MPT_000393.2023'!K34</f>
@@ -4059,7 +4137,7 @@
       </c>
       <c r="J21" s="6" t="n">
         <f aca="false">'16_MPT_000393.2023'!L34</f>
-        <v>208379.655</v>
+        <v>185071.443408</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>83</v>
@@ -4088,16 +4166,16 @@
         <v>87</v>
       </c>
       <c r="H22" s="6" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!J61</f>
-        <v>280956.101843802</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!J36</f>
+        <v>188931.0221946</v>
       </c>
       <c r="I22" s="6" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!K61</f>
-        <v>579542.1533968</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!K36</f>
+        <v>289593.2345636</v>
       </c>
       <c r="J22" s="6" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!L61</f>
-        <v>1434218.259375</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!L36</f>
+        <v>451991.7261216</v>
       </c>
       <c r="K22" s="5" t="s">
         <v>88</v>
@@ -4127,7 +4205,7 @@
       </c>
       <c r="H23" s="6" t="n">
         <f aca="false">'18_TJBA_8003152-18.2022'!J39</f>
-        <v>315078.62789676</v>
+        <v>318687.806159457</v>
       </c>
       <c r="I23" s="6" t="n">
         <f aca="false">'18_TJBA_8003152-18.2022'!K39</f>
@@ -4135,7 +4213,7 @@
       </c>
       <c r="J23" s="6" t="n">
         <f aca="false">'18_TJBA_8003152-18.2022'!L39</f>
-        <v>1380290.18559816</v>
+        <v>1221880.99603967</v>
       </c>
       <c r="K23" s="5" t="s">
         <v>92</v>
@@ -4165,7 +4243,7 @@
       </c>
       <c r="H24" s="6" t="n">
         <f aca="false">'19_TJBA_8005263-04.2024'!J52</f>
-        <v>307680.84760686</v>
+        <v>311205.285409715</v>
       </c>
       <c r="I24" s="6" t="n">
         <f aca="false">'19_TJBA_8005263-04.2024'!K52</f>
@@ -4173,7 +4251,7 @@
       </c>
       <c r="J24" s="6" t="n">
         <f aca="false">'19_TJBA_8005263-04.2024'!L52</f>
-        <v>1748983.4844538</v>
+        <v>1548261.15866009</v>
       </c>
       <c r="K24" s="5" t="s">
         <v>96</v>
@@ -4203,7 +4281,7 @@
       </c>
       <c r="H25" s="6" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!J28</f>
-        <v>25781.30861922</v>
+        <v>26162.65089396</v>
       </c>
       <c r="I25" s="6" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!K28</f>
@@ -4211,7 +4289,7 @@
       </c>
       <c r="J25" s="6" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!L28</f>
-        <v>64526.214225</v>
+        <v>57308.66386296</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>100</v>
@@ -4241,7 +4319,7 @@
       </c>
       <c r="H26" s="6" t="n">
         <f aca="false">21_TCM_03973e23!J55</f>
-        <v>385923.81394875</v>
+        <v>391632.1768275</v>
       </c>
       <c r="I26" s="6" t="n">
         <f aca="false">21_TCM_03973e23!K55</f>
@@ -4249,7 +4327,7 @@
       </c>
       <c r="J26" s="6" t="n">
         <f aca="false">21_TCM_03973e23!L55</f>
-        <v>1448377.7933625</v>
+        <v>1286370.15363948</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>105</v>
@@ -4279,7 +4357,7 @@
       </c>
       <c r="H27" s="6" t="n">
         <f aca="false">22_SN_CAMPO_DO_RODAO!J63</f>
-        <v>278660.2853727</v>
+        <v>282782.0678886</v>
       </c>
       <c r="I27" s="6" t="n">
         <f aca="false">22_SN_CAMPO_DO_RODAO!K63</f>
@@ -4287,7 +4365,7 @@
       </c>
       <c r="J27" s="6" t="n">
         <f aca="false">22_SN_CAMPO_DO_RODAO!L63</f>
-        <v>651156.78925</v>
+        <v>578321.9425688</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>109</v>
@@ -4317,7 +4395,7 @@
       </c>
       <c r="H28" s="6" t="n">
         <f aca="false">'23_TJBA_0001568-38.2011'!J64</f>
-        <v>1348883.22675834</v>
+        <v>1364334.48111168</v>
       </c>
       <c r="I28" s="6" t="n">
         <f aca="false">'23_TJBA_0001568-38.2011'!K64</f>
@@ -4325,7 +4403,7 @@
       </c>
       <c r="J28" s="6" t="n">
         <f aca="false">'23_TJBA_0001568-38.2011'!L64</f>
-        <v>7453266.74352753</v>
+        <v>6597891.57914224</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>113</v>
@@ -4355,7 +4433,7 @@
       </c>
       <c r="H29" s="6" t="n">
         <f aca="false">'24_TJBA_8007670-17.2023'!J33</f>
-        <v>584464.7078424</v>
+        <v>593109.7733232</v>
       </c>
       <c r="I29" s="6" t="n">
         <f aca="false">'24_TJBA_8007670-17.2023'!K33</f>
@@ -4363,7 +4441,7 @@
       </c>
       <c r="J29" s="6" t="n">
         <f aca="false">'24_TJBA_8007670-17.2023'!L33</f>
-        <v>4943798.2385</v>
+        <v>4390811.9337136</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>117</v>
@@ -4386,55 +4464,55 @@
         <v>86</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="H30" s="6" t="n">
-        <f aca="false">'25_TJBA_8008589-69.2024'!J55</f>
-        <v>44832.488860698</v>
+        <f aca="false">'25_TJBA_0000917-10.2015'!J28</f>
+        <v>422293.79336718</v>
       </c>
       <c r="I30" s="6" t="n">
-        <f aca="false">'25_TJBA_8008589-69.2024'!K55</f>
-        <v>140931.3818968</v>
+        <f aca="false">'25_TJBA_0000917-10.2015'!K28</f>
+        <v>737185.86135612</v>
       </c>
       <c r="J30" s="6" t="n">
-        <f aca="false">'25_TJBA_8008589-69.2024'!L55</f>
-        <v>454217.256625</v>
+        <f aca="false">'25_TJBA_0000917-10.2015'!L28</f>
+        <v>1078876.36932082</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G31" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H31" s="8" t="n">
         <f aca="false">SUM(H6:H30)</f>
-        <v>17889012.2543335</v>
+        <v>18418542.9693556</v>
       </c>
       <c r="I31" s="8" t="n">
         <f aca="false">SUM(I6:I30)</f>
-        <v>27738467.189003</v>
+        <v>28044772.7496291</v>
       </c>
       <c r="J31" s="8" t="n">
         <f aca="false">SUM(J6:J30)</f>
-        <v>53729775.8237985</v>
+        <v>47522432.9230871</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>10</v>
@@ -4456,15 +4534,15 @@
       </c>
       <c r="H35" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A35,H$6:H$30)</f>
-        <v>15910831.830872</v>
+        <v>16038804.9215536</v>
       </c>
       <c r="I35" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A35,I$6:I$30)</f>
-        <v>23074879.2792008</v>
+        <v>22784930.3603676</v>
       </c>
       <c r="J35" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A35,J$6:J$30)</f>
-        <v>40878493.585146</v>
+        <v>35454853.0409104</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4477,37 +4555,37 @@
       </c>
       <c r="H36" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A36,H$6:H$30)</f>
-        <v>1978180.42346144</v>
+        <v>2379738.04780206</v>
       </c>
       <c r="I36" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A36,I$6:I$30)</f>
-        <v>4663587.90980224</v>
+        <v>5259842.38926156</v>
       </c>
       <c r="J36" s="11" t="n">
         <f aca="false">SUMIF($E$6:$E$30,$A36,J$6:J$30)</f>
-        <v>12851282.2386525</v>
+        <v>12067579.8821767</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H37" s="13" t="n">
         <f aca="false">SUM(H35:H36)</f>
-        <v>17889012.2543335</v>
+        <v>18418542.9693556</v>
       </c>
       <c r="I37" s="13" t="n">
         <f aca="false">SUM(I35:I36)</f>
-        <v>27738467.189003</v>
+        <v>28044772.7496291</v>
       </c>
       <c r="J37" s="13" t="n">
         <f aca="false">SUM(J35:J36)</f>
-        <v>53729775.8237985</v>
+        <v>47522432.9230871</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4515,22 +4593,22 @@
         <v>84</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H40" s="14" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!J61</f>
-        <v>280956.101843802</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!J36</f>
+        <v>188931.0221946</v>
       </c>
       <c r="I40" s="14" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!K61</f>
-        <v>579542.1533968</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!K36</f>
+        <v>289593.2345636</v>
       </c>
       <c r="J40" s="14" t="n">
-        <f aca="false">'17_TJBA_0006323-71.2012'!L61</f>
-        <v>1434218.259375</v>
+        <f aca="false">'17_TJBA_0006323-71.2012'!L36</f>
+        <v>451991.7261216</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>88</v>
@@ -4541,14 +4619,14 @@
         <v>97</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>130</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!J28</f>
-        <v>25781.30861922</v>
+        <v>26162.65089396</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!K28</f>
@@ -4556,7 +4634,7 @@
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">'20_TJBA_8005837-61.2023'!L28</f>
-        <v>64526.214225</v>
+        <v>57308.66386296</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>100</v>
@@ -4574,7 +4652,7 @@
       </c>
       <c r="H42" s="14" t="n">
         <f aca="false">21_TCM_03973e23!J55</f>
-        <v>385923.81394875</v>
+        <v>391632.1768275</v>
       </c>
       <c r="I42" s="14" t="n">
         <f aca="false">21_TCM_03973e23!K55</f>
@@ -4582,7 +4660,7 @@
       </c>
       <c r="J42" s="14" t="n">
         <f aca="false">21_TCM_03973e23!L55</f>
-        <v>1448377.7933625</v>
+        <v>1286370.15363948</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>105</v>
@@ -4595,10 +4673,10 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H45" s="9" t="s">
         <v>10</v>
@@ -4620,7 +4698,7 @@
       </c>
       <c r="H46" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A46,H$6:H$30)</f>
-        <v>4026213.48582298</v>
+        <v>4076654.84807795</v>
       </c>
       <c r="I46" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A46,I$6:I$30)</f>
@@ -4628,7 +4706,7 @@
       </c>
       <c r="J46" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A46,J$6:J$30)</f>
-        <v>12797819.5798316</v>
+        <v>11346040.7956717</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4641,7 +4719,7 @@
       </c>
       <c r="H47" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A47,H$6:H$30)</f>
-        <v>10080131.0805953</v>
+        <v>10229230.576386</v>
       </c>
       <c r="I47" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A47,I$6:I$30)</f>
@@ -4649,7 +4727,7 @@
       </c>
       <c r="J47" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A47,J$6:J$30)</f>
-        <v>19348040.713925</v>
+        <v>17183874.4144329</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4662,7 +4740,7 @@
       </c>
       <c r="H48" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A48,H$6:H$30)</f>
-        <v>210406.279165698</v>
+        <v>213518.487715764</v>
       </c>
       <c r="I48" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A48,I$6:I$30)</f>
@@ -4670,7 +4748,7 @@
       </c>
       <c r="J48" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A48,J$6:J$30)</f>
-        <v>2005080.565125</v>
+        <v>1780803.1899132</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4683,15 +4761,15 @@
       </c>
       <c r="H49" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A49,H$6:H$30)</f>
-        <v>2907677.30942808</v>
+        <v>3224724.81245979</v>
       </c>
       <c r="I49" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A49,I$6:I$30)</f>
-        <v>6492958.7747887</v>
+        <v>6799264.33541482</v>
       </c>
       <c r="J49" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A49,J$6:J$30)</f>
-        <v>17479300.3823045</v>
+        <v>15347022.426861</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4704,7 +4782,7 @@
       </c>
       <c r="H50" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A50,H$6:H$30)</f>
-        <v>385923.81394875</v>
+        <v>391632.1768275</v>
       </c>
       <c r="I50" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A50,I$6:I$30)</f>
@@ -4712,7 +4790,7 @@
       </c>
       <c r="J50" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A50,J$6:J$30)</f>
-        <v>1448377.7933625</v>
+        <v>1286370.15363948</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4725,7 +4803,7 @@
       </c>
       <c r="H51" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A51,H$6:H$30)</f>
-        <v>278660.2853727</v>
+        <v>282782.0678886</v>
       </c>
       <c r="I51" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A51,I$6:I$30)</f>
@@ -4733,7 +4811,7 @@
       </c>
       <c r="J51" s="11" t="n">
         <f aca="false">SUMIF($D$6:$D$30,$A51,J$6:J$30)</f>
-        <v>651156.78925</v>
+        <v>578321.9425688</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4742,15 +4820,15 @@
       </c>
       <c r="H52" s="15" t="n">
         <f aca="false">SUM(H46:H51)</f>
-        <v>17889012.2543335</v>
+        <v>18418542.9693556</v>
       </c>
       <c r="I52" s="15" t="n">
         <f aca="false">SUM(I46:I51)</f>
-        <v>27738467.189003</v>
+        <v>28044772.7496291</v>
       </c>
       <c r="J52" s="15" t="n">
         <f aca="false">SUM(J46:J51)</f>
-        <v>53729775.8237985</v>
+        <v>47522432.9230871</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4760,10 +4838,10 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H55" s="9" t="s">
         <v>10</v>
@@ -4781,19 +4859,19 @@
       </c>
       <c r="G56" s="10" t="n">
         <f aca="false">COUNTIF($F$6:$F$30,A56)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H56" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A56,H$6:H$30)</f>
-        <v>267903.883683282</v>
+        <v>226370.938472112</v>
       </c>
       <c r="I56" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A56,I$6:I$30)</f>
-        <v>799423.903220008</v>
+        <v>658492.521323208</v>
       </c>
       <c r="J56" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A56,J$6:J$30)</f>
-        <v>2886251.05692688</v>
+        <v>2159999.76503902</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4806,7 +4884,7 @@
       </c>
       <c r="H57" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A57,H$6:H$30)</f>
-        <v>2346606.91414288</v>
+        <v>2381316.57267017</v>
       </c>
       <c r="I57" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A57,I$6:I$30)</f>
@@ -4814,7 +4892,7 @@
       </c>
       <c r="J57" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A57,J$6:J$30)</f>
-        <v>9511568.592075</v>
+        <v>8447656.41064872</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4827,7 +4905,7 @@
       </c>
       <c r="H58" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A58,H$6:H$30)</f>
-        <v>3046043.84672952</v>
+        <v>3080935.82055911</v>
       </c>
       <c r="I58" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A58,I$6:I$30)</f>
@@ -4835,7 +4913,7 @@
       </c>
       <c r="J58" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A58,J$6:J$30)</f>
-        <v>8349494.04708533</v>
+        <v>7391263.23517166</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4848,15 +4926,15 @@
       </c>
       <c r="H59" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A59,H$6:H$30)</f>
-        <v>1197839.1626452</v>
+        <v>1119376.0893798</v>
       </c>
       <c r="I59" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A59,I$6:I$30)</f>
-        <v>1861491.66036592</v>
+        <v>1571542.74153272</v>
       </c>
       <c r="J59" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A59,J$6:J$30)</f>
-        <v>3252107.381875</v>
+        <v>2066541.6871376</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4869,7 +4947,7 @@
       </c>
       <c r="H60" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A60,H$6:H$30)</f>
-        <v>1912929.80508907</v>
+        <v>1941224.7614881</v>
       </c>
       <c r="I60" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A60,I$6:I$30)</f>
@@ -4877,7 +4955,7 @@
       </c>
       <c r="J60" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A60,J$6:J$30)</f>
-        <v>9775812.534455</v>
+        <v>8682343.46696469</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4890,7 +4968,7 @@
       </c>
       <c r="H61" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A61,H$6:H$30)</f>
-        <v>7461124.56767832</v>
+        <v>7571485.22689776</v>
       </c>
       <c r="I61" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A61,I$6:I$30)</f>
@@ -4898,7 +4976,7 @@
       </c>
       <c r="J61" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A61,J$6:J$30)</f>
-        <v>10752291.9834</v>
+        <v>9549599.25100224</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4911,7 +4989,7 @@
       </c>
       <c r="H62" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A62,H$6:H$30)</f>
-        <v>1656564.0743652</v>
+        <v>1675539.76652139</v>
       </c>
       <c r="I62" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A62,I$6:I$30)</f>
@@ -4919,53 +4997,74 @@
       </c>
       <c r="J62" s="11" t="n">
         <f aca="false">SUMIF($F$6:$F$30,$A62,J$6:J$30)</f>
-        <v>9202250.22798133</v>
+        <v>8146152.73780233</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G63" s="10" t="n">
+        <f aca="false">COUNTIF($F$6:$F$30,A63)</f>
+        <v>1</v>
+      </c>
+      <c r="H63" s="11" t="n">
+        <f aca="false">SUMIF($F$6:$F$30,$A63,H$6:H$30)</f>
+        <v>422293.79336718</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <f aca="false">SUMIF($F$6:$F$30,$A63,I$6:I$30)</f>
+        <v>737185.86135612</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <f aca="false">SUMIF($F$6:$F$30,$A63,J$6:J$30)</f>
+        <v>1078876.36932082</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H63" s="15" t="n">
-        <f aca="false">SUM(H56:H62)</f>
-        <v>17889012.2543335</v>
-      </c>
-      <c r="I63" s="15" t="n">
-        <f aca="false">SUM(I56:I62)</f>
-        <v>27738467.189003</v>
-      </c>
-      <c r="J63" s="15" t="n">
-        <f aca="false">SUM(J56:J62)</f>
-        <v>53729775.8237985</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
-        <v>136</v>
+      <c r="H64" s="15" t="n">
+        <f aca="false">SUM(H56:H63)</f>
+        <v>18418542.9693556</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <f aca="false">SUM(I56:I63)</f>
+        <v>28044772.7496291</v>
+      </c>
+      <c r="J64" s="15" t="n">
+        <f aca="false">SUM(J56:J63)</f>
+        <v>47522432.9230871</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
         <v>141</v>
       </c>
     </row>
@@ -5947,7 +6046,7 @@
       </c>
       <c r="J36" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K36" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -5955,7 +6054,7 @@
       </c>
       <c r="L36" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5989,7 +6088,7 @@
       </c>
       <c r="L38" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5998,7 +6097,7 @@
       </c>
       <c r="J39" s="8" t="n">
         <f aca="false">J35*(1+J36)*(1+J37)*J38</f>
-        <v>160465.94404386</v>
+        <v>162304.05728249</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">K35*(1+K36)*(1+K37)*K38</f>
@@ -6006,7 +6105,7 @@
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">L35*(1+L36)*(1+L37)*L38</f>
-        <v>694200.074477024</v>
+        <v>614530.109177886</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7564,7 +7663,7 @@
       </c>
       <c r="J49" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K49" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -7572,7 +7671,7 @@
       </c>
       <c r="L49" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7606,7 +7705,7 @@
       </c>
       <c r="L51" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7615,7 +7714,7 @@
       </c>
       <c r="J52" s="8" t="n">
         <f aca="false">J48*(1+J49)*(1+J50)*J51</f>
-        <v>307680.84760686</v>
+        <v>311205.285409715</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">K48*(1+K49)*(1+K50)*K51</f>
@@ -7623,7 +7722,7 @@
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">L48*(1+L49)*(1+L50)*L51</f>
-        <v>1748983.4844538</v>
+        <v>1548261.15866009</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8306,7 +8405,7 @@
       </c>
       <c r="J30" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K30" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -8314,7 +8413,7 @@
       </c>
       <c r="L30" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8348,7 +8447,7 @@
       </c>
       <c r="L32" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8357,7 +8456,7 @@
       </c>
       <c r="J33" s="8" t="n">
         <f aca="false">J29*(1+J30)*(1+J31)*J32</f>
-        <v>1328465.09724667</v>
+        <v>1348114.9881649</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">K29*(1+K30)*(1+K31)*K32</f>
@@ -8365,7 +8464,7 @@
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">L29*(1+L30)*(1+L31)*L32</f>
-        <v>4832014.295955</v>
+        <v>4291531.53325109</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10065,7 +10164,7 @@
       </c>
       <c r="J54" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K54" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -10073,7 +10172,7 @@
       </c>
       <c r="L54" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10107,7 +10206,7 @@
       </c>
       <c r="L56" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10116,7 +10215,7 @@
       </c>
       <c r="J57" s="8" t="n">
         <f aca="false">J53*(1+J54)*(1+J55)*J56</f>
-        <v>7461124.56767832</v>
+        <v>7571485.22689776</v>
       </c>
       <c r="K57" s="8" t="n">
         <f aca="false">K53*(1+K54)*(1+K55)*K56</f>
@@ -10124,7 +10223,7 @@
       </c>
       <c r="L57" s="8" t="n">
         <f aca="false">L53*(1+L54)*(1+L55)*L56</f>
-        <v>10752291.9834</v>
+        <v>9549599.25100224</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15466,7 +15565,7 @@
       </c>
       <c r="J135" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K135" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -15474,7 +15573,7 @@
       </c>
       <c r="L135" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15508,7 +15607,7 @@
       </c>
       <c r="L137" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15517,7 +15616,7 @@
       </c>
       <c r="J138" s="8" t="n">
         <f aca="false">J134*(1+J135)*(1+J136)*J137</f>
-        <v>1290541.41567028</v>
+        <v>1309630.36132337</v>
       </c>
       <c r="K138" s="8" t="n">
         <f aca="false">K134*(1+K135)*(1+K136)*K137</f>
@@ -15525,7 +15624,7 @@
       </c>
       <c r="L138" s="8" t="n">
         <f aca="false">L134*(1+L135)*(1+L136)*L137</f>
-        <v>3763734.43457</v>
+        <v>3342743.63017955</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17122,7 +17221,7 @@
       </c>
       <c r="J49" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K49" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -17130,7 +17229,7 @@
       </c>
       <c r="L49" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17164,7 +17263,7 @@
       </c>
       <c r="L51" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17173,7 +17272,7 @@
       </c>
       <c r="J52" s="8" t="n">
         <f aca="false">J48*(1+J49)*(1+J50)*J51</f>
-        <v>43249.121929398</v>
+        <v>43888.838042364</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">K48*(1+K49)*(1+K50)*K51</f>
@@ -17181,7 +17280,7 @@
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">L48*(1+L49)*(1+L50)*L51</f>
-        <v>400710.7983175</v>
+        <v>355889.474112968</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18783,7 +18882,7 @@
       </c>
       <c r="J50" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K50" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -18791,7 +18890,7 @@
       </c>
       <c r="L50" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18825,7 +18924,7 @@
       </c>
       <c r="L52" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18834,7 +18933,7 @@
       </c>
       <c r="J53" s="8" t="n">
         <f aca="false">J49*(1+J50)*(1+J51)*J52</f>
-        <v>62764.16907915</v>
+        <v>63692.5405347</v>
       </c>
       <c r="K53" s="8" t="n">
         <f aca="false">K49*(1+K50)*(1+K51)*K52</f>
@@ -18842,7 +18941,7 @@
       </c>
       <c r="L53" s="8" t="n">
         <f aca="false">L49*(1+L50)*(1+L51)*L52</f>
-        <v>797089.8084325</v>
+        <v>707931.690223832</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20439,7 +20538,7 @@
       </c>
       <c r="J49" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K49" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -20447,7 +20546,7 @@
       </c>
       <c r="L49" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20481,7 +20580,7 @@
       </c>
       <c r="L51" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20490,7 +20589,7 @@
       </c>
       <c r="J52" s="8" t="n">
         <f aca="false">J48*(1+J49)*(1+J50)*J51</f>
-        <v>62764.16907915</v>
+        <v>63692.5405347</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">K48*(1+K49)*(1+K50)*K51</f>
@@ -20498,7 +20597,7 @@
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">L48*(1+L49)*(1+L50)*L51</f>
-        <v>598900.303375</v>
+        <v>531910.5821684</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21264,7 +21363,7 @@
       </c>
       <c r="J31" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K31" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -21272,7 +21371,7 @@
       </c>
       <c r="L31" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21306,7 +21405,7 @@
       </c>
       <c r="L33" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21315,7 +21414,7 @@
       </c>
       <c r="J34" s="8" t="n">
         <f aca="false">J30*(1+J31)*(1+J32)*J33</f>
-        <v>41628.819078</v>
+        <v>42244.568604</v>
       </c>
       <c r="K34" s="8" t="n">
         <f aca="false">K30*(1+K31)*(1+K32)*K33</f>
@@ -21323,7 +21422,7 @@
       </c>
       <c r="L34" s="8" t="n">
         <f aca="false">L30*(1+L31)*(1+L32)*L33</f>
-        <v>208379.655</v>
+        <v>185071.443408</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21347,7 +21446,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -21453,182 +21552,143 @@
         <v>747</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="20" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C17" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I17" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J17" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L17" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M17" s="4" t="s">
         <v>183</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>750</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>388.09</v>
-      </c>
-      <c r="G17" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="I17" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="J17" s="22" t="n">
-        <f aca="false">F17*G17</f>
-        <v>5821.35</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <f aca="false">F17*H17</f>
-        <v>7761.8</v>
-      </c>
-      <c r="L17" s="22" t="n">
-        <f aca="false">F17*I17</f>
-        <v>11642.7</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>308</v>
+        <v>750</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>309</v>
+        <v>751</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>277</v>
       </c>
       <c r="F18" s="21" t="n">
-        <v>17.96</v>
+        <v>388.09</v>
       </c>
       <c r="G18" s="21" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H18" s="21" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="I18" s="21" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J18" s="22" t="n">
         <f aca="false">F18*G18</f>
-        <v>718.4</v>
+        <v>5821.35</v>
       </c>
       <c r="K18" s="22" t="n">
         <f aca="false">F18*H18</f>
-        <v>1077.6</v>
+        <v>7761.8</v>
       </c>
       <c r="L18" s="22" t="n">
         <f aca="false">F18*I18</f>
-        <v>1616.4</v>
+        <v>11642.7</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>310</v>
+        <v>752</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>277</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>33</v>
+        <v>255.6</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J19" s="22" t="n">
         <f aca="false">F19*G19</f>
-        <v>1320</v>
+        <v>2556</v>
       </c>
       <c r="K19" s="22" t="n">
         <f aca="false">F19*H19</f>
-        <v>1980</v>
+        <v>3834</v>
       </c>
       <c r="L19" s="22" t="n">
         <f aca="false">F19*I19</f>
-        <v>2970</v>
+        <v>5112</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>756</v>
@@ -21640,31 +21700,31 @@
         <v>757</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>474.61</v>
+        <v>808.1</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>300</v>
+        <v>3</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>450</v>
+        <v>4</v>
       </c>
       <c r="J20" s="22" t="n">
         <f aca="false">F20*G20</f>
-        <v>94922</v>
+        <v>1616.2</v>
       </c>
       <c r="K20" s="22" t="n">
         <f aca="false">F20*H20</f>
-        <v>142383</v>
+        <v>2424.3</v>
       </c>
       <c r="L20" s="22" t="n">
         <f aca="false">F20*I20</f>
-        <v>213574.5</v>
+        <v>3232.4</v>
       </c>
       <c r="M20" s="5" t="s">
         <v>758</v>
@@ -21675,43 +21735,43 @@
         <v>759</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>760</v>
+        <v>308</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>761</v>
+        <v>309</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>277</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>148.57</v>
+        <v>17.96</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="J21" s="22" t="n">
         <f aca="false">F21*G21</f>
-        <v>891.42</v>
+        <v>718.4</v>
       </c>
       <c r="K21" s="22" t="n">
         <f aca="false">F21*H21</f>
-        <v>1188.56</v>
+        <v>1077.6</v>
       </c>
       <c r="L21" s="22" t="n">
         <f aca="false">F21*I21</f>
-        <v>1782.84</v>
+        <v>1616.4</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21719,1628 +21779,528 @@
         <v>759</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>194</v>
+        <v>277</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>111.74</v>
+        <v>33</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>300</v>
+        <v>40</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="J22" s="22" t="n">
         <f aca="false">F22*G22</f>
-        <v>33522</v>
+        <v>1320</v>
       </c>
       <c r="K22" s="22" t="n">
         <f aca="false">F22*H22</f>
-        <v>44696</v>
+        <v>1980</v>
       </c>
       <c r="L22" s="22" t="n">
         <f aca="false">F22*I22</f>
-        <v>67044</v>
+        <v>2970</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>265</v>
+        <v>764</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>266</v>
+        <v>765</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>12.33</v>
+        <v>34.84</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>2000</v>
+        <v>15</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>3000</v>
+        <v>20</v>
       </c>
       <c r="J23" s="22" t="n">
         <f aca="false">F23*G23</f>
-        <v>18495</v>
+        <v>348.4</v>
       </c>
       <c r="K23" s="22" t="n">
         <f aca="false">F23*H23</f>
-        <v>24660</v>
+        <v>522.6</v>
       </c>
       <c r="L23" s="22" t="n">
         <f aca="false">F23*I23</f>
-        <v>36990</v>
+        <v>696.8</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>768</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>769</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>188</v>
+        <v>770</v>
       </c>
       <c r="F24" s="21" t="n">
-        <v>154.44</v>
+        <v>1459.9</v>
       </c>
       <c r="G24" s="21" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H24" s="21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I24" s="21" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J24" s="22" t="n">
         <f aca="false">F24*G24</f>
-        <v>1544.4</v>
+        <v>2919.8</v>
       </c>
       <c r="K24" s="22" t="n">
         <f aca="false">F24*H24</f>
-        <v>3088.8</v>
+        <v>5839.6</v>
       </c>
       <c r="L24" s="22" t="n">
         <f aca="false">F24*I24</f>
-        <v>4633.2</v>
+        <v>8759.4</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>216</v>
+        <v>773</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>217</v>
+        <v>774</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F25" s="21" t="n">
-        <v>454.97</v>
+        <v>474.61</v>
       </c>
       <c r="G25" s="21" t="n">
-        <v>6</v>
+        <v>200</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="I25" s="21" t="n">
-        <v>6</v>
+        <v>450</v>
       </c>
       <c r="J25" s="22" t="n">
         <f aca="false">F25*G25</f>
-        <v>2729.82</v>
+        <v>94922</v>
       </c>
       <c r="K25" s="22" t="n">
         <f aca="false">F25*H25</f>
-        <v>2729.82</v>
+        <v>142383</v>
       </c>
       <c r="L25" s="22" t="n">
         <f aca="false">F25*I25</f>
-        <v>2729.82</v>
+        <v>213574.5</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>218</v>
+        <v>775</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>220</v>
+        <v>777</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>221</v>
+        <v>778</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F26" s="21" t="n">
-        <v>4.43</v>
+        <v>148.57</v>
       </c>
       <c r="G26" s="21" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>375</v>
+        <v>8</v>
       </c>
       <c r="I26" s="21" t="n">
-        <v>1125</v>
+        <v>12</v>
       </c>
       <c r="J26" s="22" t="n">
         <f aca="false">F26*G26</f>
-        <v>443</v>
+        <v>891.42</v>
       </c>
       <c r="K26" s="22" t="n">
         <f aca="false">F26*H26</f>
-        <v>1661.25</v>
+        <v>1188.56</v>
       </c>
       <c r="L26" s="22" t="n">
         <f aca="false">F26*I26</f>
-        <v>4983.75</v>
+        <v>1782.84</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>222</v>
+        <v>779</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>223</v>
+        <v>780</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>224</v>
+        <v>781</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F27" s="21" t="n">
-        <v>9.56</v>
+        <v>111.74</v>
       </c>
       <c r="G27" s="21" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>187.5</v>
+        <v>400</v>
       </c>
       <c r="I27" s="21" t="n">
-        <v>562.5</v>
+        <v>600</v>
       </c>
       <c r="J27" s="22" t="n">
         <f aca="false">F27*G27</f>
-        <v>478</v>
+        <v>33522</v>
       </c>
       <c r="K27" s="22" t="n">
         <f aca="false">F27*H27</f>
-        <v>1792.5</v>
+        <v>44696</v>
       </c>
       <c r="L27" s="22" t="n">
         <f aca="false">F27*I27</f>
-        <v>5377.5</v>
+        <v>67044</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>225</v>
+        <v>782</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>226</v>
+        <v>783</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>227</v>
+        <v>784</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F28" s="21" t="n">
-        <v>2.58</v>
+        <v>132.73</v>
       </c>
       <c r="G28" s="21" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>300</v>
+        <v>8</v>
       </c>
       <c r="I28" s="21" t="n">
-        <v>900</v>
+        <v>12</v>
       </c>
       <c r="J28" s="22" t="n">
         <f aca="false">F28*G28</f>
-        <v>206.4</v>
+        <v>796.38</v>
       </c>
       <c r="K28" s="22" t="n">
         <f aca="false">F28*H28</f>
-        <v>774</v>
+        <v>1061.84</v>
       </c>
       <c r="L28" s="22" t="n">
         <f aca="false">F28*I28</f>
-        <v>2322</v>
+        <v>1592.76</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>228</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>229</v>
+        <v>786</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>230</v>
+        <v>787</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F29" s="21" t="n">
-        <v>10.04</v>
+        <v>54.46</v>
       </c>
       <c r="G29" s="21" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="H29" s="21" t="n">
-        <v>180</v>
+        <v>8</v>
       </c>
       <c r="I29" s="21" t="n">
-        <v>540</v>
+        <v>12</v>
       </c>
       <c r="J29" s="22" t="n">
         <f aca="false">F29*G29</f>
-        <v>401.6</v>
+        <v>326.76</v>
       </c>
       <c r="K29" s="22" t="n">
         <f aca="false">F29*H29</f>
-        <v>1807.2</v>
+        <v>435.68</v>
       </c>
       <c r="L29" s="22" t="n">
         <f aca="false">F29*I29</f>
-        <v>5421.6</v>
+        <v>653.52</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>231</v>
+        <v>788</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>232</v>
+        <v>292</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F30" s="21" t="n">
-        <v>28.42</v>
+        <v>623.29</v>
       </c>
       <c r="G30" s="21" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H30" s="21" t="n">
-        <v>54</v>
+        <v>3</v>
       </c>
       <c r="I30" s="21" t="n">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="J30" s="22" t="n">
         <f aca="false">F30*G30</f>
-        <v>341.04</v>
+        <v>1246.58</v>
       </c>
       <c r="K30" s="22" t="n">
         <f aca="false">F30*H30</f>
-        <v>1534.68</v>
+        <v>1869.87</v>
       </c>
       <c r="L30" s="22" t="n">
         <f aca="false">F30*I30</f>
-        <v>4604.04</v>
+        <v>2493.16</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>234</v>
+        <v>790</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>235</v>
+        <v>791</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>236</v>
+        <v>792</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>188</v>
+        <v>277</v>
       </c>
       <c r="F31" s="21" t="n">
-        <v>30.78</v>
+        <v>168.46</v>
       </c>
       <c r="G31" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H31" s="21" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="I31" s="21" t="n">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="J31" s="22" t="n">
         <f aca="false">F31*G31</f>
-        <v>184.68</v>
+        <v>336.92</v>
       </c>
       <c r="K31" s="22" t="n">
         <f aca="false">F31*H31</f>
-        <v>831.06</v>
+        <v>505.38</v>
       </c>
       <c r="L31" s="22" t="n">
         <f aca="false">F31*I31</f>
-        <v>2493.18</v>
+        <v>673.84</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>237</v>
+        <v>793</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>101.54</v>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>562.5</v>
-      </c>
-      <c r="J32" s="22" t="n">
-        <f aca="false">F32*G32</f>
-        <v>5077</v>
-      </c>
-      <c r="K32" s="22" t="n">
-        <f aca="false">F32*H32</f>
-        <v>19038.75</v>
-      </c>
-      <c r="L32" s="22" t="n">
-        <f aca="false">F32*I32</f>
-        <v>57116.25</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>241</v>
+      <c r="I32" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="J32" s="23" t="n">
+        <f aca="false">SUM(J18:J31)</f>
+        <v>147342.21</v>
+      </c>
+      <c r="K32" s="23" t="n">
+        <f aca="false">SUM(K18:K31)</f>
+        <v>215580.23</v>
+      </c>
+      <c r="L32" s="23" t="n">
+        <f aca="false">SUM(L18:L31)</f>
+        <v>321844.32</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="G33" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="H33" s="21" t="n">
-        <v>375</v>
-      </c>
-      <c r="I33" s="21" t="n">
-        <v>1125</v>
-      </c>
-      <c r="J33" s="22" t="n">
-        <f aca="false">F33*G33</f>
-        <v>4242</v>
-      </c>
-      <c r="K33" s="22" t="n">
-        <f aca="false">F33*H33</f>
-        <v>15907.5</v>
-      </c>
-      <c r="L33" s="22" t="n">
-        <f aca="false">F33*I33</f>
-        <v>47722.5</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>773</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>80</v>
-      </c>
-      <c r="H34" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="I34" s="21" t="n">
-        <v>900</v>
-      </c>
-      <c r="J34" s="22" t="n">
-        <f aca="false">F34*G34</f>
-        <v>5856</v>
-      </c>
-      <c r="K34" s="22" t="n">
-        <f aca="false">F34*H34</f>
-        <v>21960</v>
-      </c>
-      <c r="L34" s="22" t="n">
-        <f aca="false">F34*I34</f>
-        <v>65880</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="G35" s="21" t="n">
-        <v>96</v>
-      </c>
-      <c r="H35" s="21" t="n">
-        <v>432</v>
-      </c>
-      <c r="I35" s="21" t="n">
-        <v>1296</v>
-      </c>
-      <c r="J35" s="22" t="n">
-        <f aca="false">F35*G35</f>
-        <v>578.88</v>
-      </c>
-      <c r="K35" s="22" t="n">
-        <f aca="false">F35*H35</f>
-        <v>2604.96</v>
-      </c>
-      <c r="L35" s="22" t="n">
-        <f aca="false">F35*I35</f>
-        <v>7814.88</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>96</v>
-      </c>
-      <c r="H36" s="21" t="n">
-        <v>432</v>
-      </c>
-      <c r="I36" s="21" t="n">
-        <v>1296</v>
-      </c>
-      <c r="J36" s="22" t="n">
-        <f aca="false">F36*G36</f>
-        <v>3051.84</v>
-      </c>
-      <c r="K36" s="22" t="n">
-        <f aca="false">F36*H36</f>
-        <v>13733.28</v>
-      </c>
-      <c r="L36" s="22" t="n">
-        <f aca="false">F36*I36</f>
-        <v>41199.84</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G37" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="H37" s="21" t="n">
-        <v>54</v>
-      </c>
-      <c r="I37" s="21" t="n">
-        <v>162</v>
-      </c>
-      <c r="J37" s="22" t="n">
-        <f aca="false">F37*G37</f>
-        <v>711.6</v>
-      </c>
-      <c r="K37" s="22" t="n">
-        <f aca="false">F37*H37</f>
-        <v>3202.2</v>
-      </c>
-      <c r="L37" s="22" t="n">
-        <f aca="false">F37*I37</f>
-        <v>9606.6</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="H38" s="21" t="n">
-        <v>180</v>
-      </c>
-      <c r="I38" s="21" t="n">
-        <v>540</v>
-      </c>
-      <c r="J38" s="22" t="n">
-        <f aca="false">F38*G38</f>
-        <v>2327.6</v>
-      </c>
-      <c r="K38" s="22" t="n">
-        <f aca="false">F38*H38</f>
-        <v>10474.2</v>
-      </c>
-      <c r="L38" s="22" t="n">
-        <f aca="false">F38*I38</f>
-        <v>31422.6</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F39" s="21" t="n">
-        <v>50.14</v>
-      </c>
-      <c r="G39" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="H39" s="21" t="n">
-        <v>180</v>
-      </c>
-      <c r="I39" s="21" t="n">
-        <v>540</v>
-      </c>
-      <c r="J39" s="22" t="n">
-        <f aca="false">F39*G39</f>
-        <v>2005.6</v>
-      </c>
-      <c r="K39" s="22" t="n">
-        <f aca="false">F39*H39</f>
-        <v>9025.2</v>
-      </c>
-      <c r="L39" s="22" t="n">
-        <f aca="false">F39*I39</f>
-        <v>27075.6</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F40" s="21" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>1200</v>
-      </c>
-      <c r="H40" s="21" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I40" s="21" t="n">
-        <v>2700</v>
-      </c>
-      <c r="J40" s="22" t="n">
-        <f aca="false">F40*G40</f>
-        <v>14796</v>
-      </c>
-      <c r="K40" s="22" t="n">
-        <f aca="false">F40*H40</f>
-        <v>22194</v>
-      </c>
-      <c r="L40" s="22" t="n">
-        <f aca="false">F40*I40</f>
-        <v>33291</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F41" s="21" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="G41" s="21" t="n">
-        <v>120</v>
-      </c>
-      <c r="H41" s="21" t="n">
-        <v>180</v>
-      </c>
-      <c r="I41" s="21" t="n">
-        <v>270</v>
-      </c>
-      <c r="J41" s="22" t="n">
-        <f aca="false">F41*G41</f>
-        <v>1830</v>
-      </c>
-      <c r="K41" s="22" t="n">
-        <f aca="false">F41*H41</f>
-        <v>2745</v>
-      </c>
-      <c r="L41" s="22" t="n">
-        <f aca="false">F41*I41</f>
-        <v>4117.5</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F42" s="21" t="n">
-        <v>223.25</v>
-      </c>
-      <c r="G42" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H42" s="21" t="n">
-        <v>27</v>
-      </c>
-      <c r="I42" s="21" t="n">
-        <v>81</v>
-      </c>
-      <c r="J42" s="22" t="n">
-        <f aca="false">F42*G42</f>
-        <v>1339.5</v>
-      </c>
-      <c r="K42" s="22" t="n">
-        <f aca="false">F42*H42</f>
-        <v>6027.75</v>
-      </c>
-      <c r="L42" s="22" t="n">
-        <f aca="false">F42*I42</f>
-        <v>18083.25</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>776</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F43" s="21" t="n">
-        <v>1179.17</v>
-      </c>
-      <c r="G43" s="21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H43" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I43" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="J43" s="22" t="n">
-        <f aca="false">F43*G43</f>
-        <v>3148.3839</v>
-      </c>
-      <c r="K43" s="22" t="n">
-        <f aca="false">F43*H43</f>
-        <v>14150.04</v>
-      </c>
-      <c r="L43" s="22" t="n">
-        <f aca="false">F43*I43</f>
-        <v>42450.12</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F44" s="21" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="G44" s="21" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="H44" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="I44" s="21" t="n">
-        <v>150</v>
-      </c>
-      <c r="J44" s="22" t="n">
-        <f aca="false">F44*G44</f>
-        <v>715.6877</v>
-      </c>
-      <c r="K44" s="22" t="n">
-        <f aca="false">F44*H44</f>
-        <v>2684.5</v>
-      </c>
-      <c r="L44" s="22" t="n">
-        <f aca="false">F44*I44</f>
-        <v>8053.5</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F45" s="21" t="n">
-        <v>30.86</v>
-      </c>
-      <c r="G45" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" s="21" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="I45" s="21" t="n">
-        <v>112.5</v>
-      </c>
-      <c r="J45" s="22" t="n">
-        <f aca="false">F45*G45</f>
-        <v>308.6</v>
-      </c>
-      <c r="K45" s="22" t="n">
-        <f aca="false">F45*H45</f>
-        <v>1157.25</v>
-      </c>
-      <c r="L45" s="22" t="n">
-        <f aca="false">F45*I45</f>
-        <v>3471.75</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>960</v>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>3600</v>
-      </c>
-      <c r="I46" s="21" t="n">
-        <v>10800</v>
-      </c>
-      <c r="J46" s="22" t="n">
-        <f aca="false">F46*G46</f>
-        <v>5260.8</v>
-      </c>
-      <c r="K46" s="22" t="n">
-        <f aca="false">F46*H46</f>
-        <v>19728</v>
-      </c>
-      <c r="L46" s="22" t="n">
-        <f aca="false">F46*I46</f>
-        <v>59184</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G47" s="21" t="n">
-        <v>320</v>
-      </c>
-      <c r="H47" s="21" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I47" s="21" t="n">
-        <v>3600</v>
-      </c>
-      <c r="J47" s="22" t="n">
-        <f aca="false">F47*G47</f>
-        <v>3584</v>
-      </c>
-      <c r="K47" s="22" t="n">
-        <f aca="false">F47*H47</f>
-        <v>13440</v>
-      </c>
-      <c r="L47" s="22" t="n">
-        <f aca="false">F47*I47</f>
-        <v>40320</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>623.29</v>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="22" t="n">
-        <f aca="false">F48*G48</f>
-        <v>623.29</v>
-      </c>
-      <c r="K48" s="22" t="n">
-        <f aca="false">F48*H48</f>
-        <v>1246.58</v>
-      </c>
-      <c r="L48" s="22" t="n">
-        <f aca="false">F48*I48</f>
-        <v>3739.74</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <v>630.3</v>
-      </c>
-      <c r="G49" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H49" s="21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I49" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J49" s="22" t="n">
-        <f aca="false">F49*G49</f>
-        <v>1260.6</v>
-      </c>
-      <c r="K49" s="22" t="n">
-        <f aca="false">F49*H49</f>
-        <v>4727.25</v>
-      </c>
-      <c r="L49" s="22" t="n">
-        <f aca="false">F49*I49</f>
-        <v>14181.75</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>368.02</v>
-      </c>
-      <c r="G50" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="21" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I50" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J50" s="22" t="n">
-        <f aca="false">F50*G50</f>
-        <v>736.04</v>
-      </c>
-      <c r="K50" s="22" t="n">
-        <f aca="false">F50*H50</f>
-        <v>2760.15</v>
-      </c>
-      <c r="L50" s="22" t="n">
-        <f aca="false">F50*I50</f>
-        <v>8280.45</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F51" s="21" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="G51" s="21" t="n">
-        <v>24</v>
-      </c>
-      <c r="H51" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I51" s="21" t="n">
-        <v>270</v>
-      </c>
-      <c r="J51" s="22" t="n">
-        <f aca="false">F51*G51</f>
-        <v>1038.24</v>
-      </c>
-      <c r="K51" s="22" t="n">
-        <f aca="false">F51*H51</f>
-        <v>3893.4</v>
-      </c>
-      <c r="L51" s="22" t="n">
-        <f aca="false">F51*I51</f>
-        <v>11680.2</v>
-      </c>
-      <c r="M51" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F52" s="21" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="G52" s="21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="H52" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="J52" s="22" t="n">
-        <f aca="false">F52*G52</f>
-        <v>769.227</v>
-      </c>
-      <c r="K52" s="22" t="n">
-        <f aca="false">F52*H52</f>
-        <v>1152.4</v>
-      </c>
-      <c r="L52" s="22" t="n">
-        <f aca="false">F52*I52</f>
-        <v>1728.6</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F53" s="21" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="G53" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="H53" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I53" s="21" t="n">
-        <v>18</v>
-      </c>
-      <c r="J53" s="22" t="n">
-        <f aca="false">F53*G53</f>
-        <v>143.68</v>
-      </c>
-      <c r="K53" s="22" t="n">
-        <f aca="false">F53*H53</f>
-        <v>215.52</v>
-      </c>
-      <c r="L53" s="22" t="n">
-        <f aca="false">F53*I53</f>
-        <v>323.28</v>
-      </c>
-      <c r="M53" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="s">
-        <v>778</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F54" s="21" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="G54" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="H54" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="I54" s="21" t="n">
-        <v>18</v>
-      </c>
-      <c r="J54" s="22" t="n">
-        <f aca="false">F54*G54</f>
-        <v>163.76</v>
-      </c>
-      <c r="K54" s="22" t="n">
-        <f aca="false">F54*H54</f>
-        <v>245.64</v>
-      </c>
-      <c r="L54" s="22" t="n">
-        <f aca="false">F54*I54</f>
-        <v>368.46</v>
-      </c>
-      <c r="M54" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F55" s="21" t="n">
-        <v>9.88</v>
-      </c>
-      <c r="G55" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="H55" s="21" t="n">
-        <v>30</v>
-      </c>
-      <c r="I55" s="21" t="n">
-        <v>45</v>
-      </c>
-      <c r="J55" s="22" t="n">
-        <f aca="false">F55*G55</f>
-        <v>197.6</v>
-      </c>
-      <c r="K55" s="22" t="n">
-        <f aca="false">F55*H55</f>
-        <v>296.4</v>
-      </c>
-      <c r="L55" s="22" t="n">
-        <f aca="false">F55*I55</f>
-        <v>444.6</v>
-      </c>
-      <c r="M55" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
-        <v>779</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F56" s="21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G56" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H56" s="21" t="n">
-        <v>300</v>
-      </c>
-      <c r="I56" s="21" t="n">
-        <v>450</v>
-      </c>
-      <c r="J56" s="22" t="n">
-        <f aca="false">F56*G56</f>
-        <v>566</v>
-      </c>
-      <c r="K56" s="22" t="n">
-        <f aca="false">F56*H56</f>
-        <v>849</v>
-      </c>
-      <c r="L56" s="22" t="n">
-        <f aca="false">F56*I56</f>
-        <v>1273.5</v>
-      </c>
-      <c r="M56" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I57" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="J57" s="23" t="n">
-        <f aca="false">SUM(J17:J56)</f>
-        <v>222351.0386</v>
-      </c>
-      <c r="K57" s="23" t="n">
-        <f aca="false">SUM(K17:K56)</f>
-        <v>431425.24</v>
-      </c>
-      <c r="L57" s="23" t="n">
-        <f aca="false">SUM(L17:L56)</f>
-        <v>907015.5</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I58" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="J58" s="24" t="n">
+      <c r="J33" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
-      </c>
-      <c r="K58" s="24" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="K33" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
         <v>0.2212</v>
       </c>
-      <c r="L58" s="24" t="n">
+      <c r="L33" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I59" s="7" t="s">
+        <v>0.2212</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="J59" s="24" t="n">
+      <c r="J34" s="24" t="n">
         <f aca="false">PARAMETROS!$B$8</f>
         <v>0.05</v>
       </c>
-      <c r="K59" s="24" t="n">
+      <c r="K34" s="24" t="n">
         <f aca="false">PARAMETROS!$C$8</f>
         <v>0.1</v>
       </c>
-      <c r="L59" s="24" t="n">
+      <c r="L34" s="24" t="n">
         <f aca="false">PARAMETROS!$D$8</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I60" s="7" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I35" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J60" s="25" t="n">
+      <c r="J35" s="25" t="n">
         <f aca="false">PARAMETROS!$B$9</f>
         <v>1</v>
       </c>
-      <c r="K60" s="25" t="n">
+      <c r="K35" s="25" t="n">
         <f aca="false">PARAMETROS!$C$9</f>
         <v>1</v>
       </c>
-      <c r="L60" s="25" t="n">
+      <c r="L35" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I61" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="J61" s="8" t="n">
-        <f aca="false">J57*(1+J58)*(1+J59)*J60</f>
-        <v>280956.101843802</v>
-      </c>
-      <c r="K61" s="8" t="n">
-        <f aca="false">K57*(1+K58)*(1+K59)*K60</f>
-        <v>579542.1533968</v>
-      </c>
-      <c r="L61" s="8" t="n">
-        <f aca="false">L57*(1+L58)*(1+L59)*L60</f>
-        <v>1434218.259375</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="26" t="s">
+      <c r="J36" s="8" t="n">
+        <f aca="false">J32*(1+J33)*(1+J34)*J35</f>
+        <v>188931.0221946</v>
+      </c>
+      <c r="K36" s="8" t="n">
+        <f aca="false">K32*(1+K33)*(1+K34)*K35</f>
+        <v>289593.2345636</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <f aca="false">L32*(1+L33)*(1+L34)*L35</f>
+        <v>451991.7261216</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="26" t="s">
         <v>327</v>
       </c>
     </row>
@@ -23405,30 +22365,30 @@
         <v>149</v>
       </c>
       <c r="B6" s="17" t="n">
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="C6" s="17" t="n">
         <v>0.2212</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B7" s="17" t="n">
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="C7" s="17" t="n">
         <v>0.2097</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
       <c r="E7" s="18" t="s">
         <v>152</v>
@@ -23462,7 +22422,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>156</v>
@@ -23510,7 +22470,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>780</v>
+        <v>794</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23555,7 +22515,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>781</v>
+        <v>795</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23587,12 +22547,12 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>782</v>
+        <v>796</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>783</v>
+        <v>797</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23726,7 +22686,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>784</v>
+        <v>798</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24210,7 +23170,7 @@
         <v>0</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>785</v>
+        <v>799</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24254,7 +23214,7 @@
         <v>21329.28</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>786</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24456,7 +23416,7 @@
       </c>
       <c r="J36" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K36" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -24464,7 +23424,7 @@
       </c>
       <c r="L36" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24498,7 +23458,7 @@
       </c>
       <c r="L38" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24507,7 +23467,7 @@
       </c>
       <c r="J39" s="8" t="n">
         <f aca="false">J35*(1+J36)*(1+J37)*J38</f>
-        <v>315078.62789676</v>
+        <v>318687.806159457</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">K35*(1+K36)*(1+K37)*K38</f>
@@ -24515,7 +23475,7 @@
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">L35*(1+L36)*(1+L37)*L38</f>
-        <v>1380290.18559816</v>
+        <v>1221880.99603967</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24555,7 +23515,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>787</v>
+        <v>801</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24600,7 +23560,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>788</v>
+        <v>802</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24632,12 +23592,12 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>789</v>
+        <v>803</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>790</v>
+        <v>804</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26073,7 +25033,7 @@
       </c>
       <c r="J49" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K49" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -26081,7 +25041,7 @@
       </c>
       <c r="L49" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26115,7 +25075,7 @@
       </c>
       <c r="L51" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26124,7 +25084,7 @@
       </c>
       <c r="J52" s="8" t="n">
         <f aca="false">J48*(1+J49)*(1+J50)*J51</f>
-        <v>307680.84760686</v>
+        <v>311205.285409715</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">K48*(1+K49)*(1+K50)*K51</f>
@@ -26132,7 +25092,7 @@
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">L48*(1+L49)*(1+L50)*L51</f>
-        <v>1748983.4844538</v>
+        <v>1548261.15866009</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26172,7 +25132,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>791</v>
+        <v>805</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26217,7 +25177,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>792</v>
+        <v>806</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26249,12 +25209,12 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>793</v>
+        <v>807</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>794</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26300,7 +25260,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>338</v>
@@ -26339,21 +25299,21 @@
         <v>413.6</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>796</v>
+        <v>810</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>317</v>
@@ -26383,12 +25343,12 @@
         <v>3821.536</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>799</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>344</v>
@@ -26427,12 +25387,12 @@
         <v>1665.6</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>800</v>
+        <v>814</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>524</v>
@@ -26471,12 +25431,12 @@
         <v>16524</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>802</v>
+        <v>816</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>801</v>
+        <v>815</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>527</v>
@@ -26515,12 +25475,12 @@
         <v>9251.04</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>803</v>
+        <v>817</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>517</v>
@@ -26559,21 +25519,21 @@
         <v>4954.08</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>805</v>
+        <v>819</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>797</v>
+        <v>811</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>798</v>
+        <v>812</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>317</v>
@@ -26603,21 +25563,21 @@
         <v>1433.076</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>806</v>
+        <v>820</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>804</v>
+        <v>818</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>807</v>
+        <v>821</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>808</v>
+        <v>822</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>188</v>
@@ -26647,7 +25607,7 @@
         <v>2744.16</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>809</v>
+        <v>823</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26673,7 +25633,7 @@
       </c>
       <c r="J25" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K25" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -26681,7 +25641,7 @@
       </c>
       <c r="L25" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26715,7 +25675,7 @@
       </c>
       <c r="L27" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26724,7 +25684,7 @@
       </c>
       <c r="J28" s="8" t="n">
         <f aca="false">J24*(1+J25)*(1+J26)*J27</f>
-        <v>25781.30861922</v>
+        <v>26162.65089396</v>
       </c>
       <c r="K28" s="8" t="n">
         <f aca="false">K24*(1+K25)*(1+K26)*K27</f>
@@ -26732,7 +25692,7 @@
       </c>
       <c r="L28" s="8" t="n">
         <f aca="false">L24*(1+L25)*(1+L26)*L27</f>
-        <v>64526.214225</v>
+        <v>57308.66386296</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26772,7 +25732,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>810</v>
+        <v>824</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26817,7 +25777,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>811</v>
+        <v>825</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26849,12 +25809,12 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>812</v>
+        <v>826</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>813</v>
+        <v>827</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28422,7 +27382,7 @@
       </c>
       <c r="J52" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K52" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -28430,7 +27390,7 @@
       </c>
       <c r="L52" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28464,7 +27424,7 @@
       </c>
       <c r="L54" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28473,7 +27433,7 @@
       </c>
       <c r="J55" s="8" t="n">
         <f aca="false">J51*(1+J52)*(1+J53)*J54</f>
-        <v>385923.81394875</v>
+        <v>391632.1768275</v>
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">K51*(1+K52)*(1+K53)*K54</f>
@@ -28481,7 +27441,7 @@
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">L51*(1+L52)*(1+L53)*L54</f>
-        <v>1448377.7933625</v>
+        <v>1286370.15363948</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28521,7 +27481,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>814</v>
+        <v>828</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28566,7 +27526,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>815</v>
+        <v>829</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28598,7 +27558,7 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>816</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28693,7 +27653,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>511</v>
@@ -28732,21 +27692,21 @@
         <v>0</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>818</v>
+        <v>832</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>819</v>
+        <v>833</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>820</v>
+        <v>834</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>194</v>
@@ -28776,12 +27736,12 @@
         <v>28416</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>821</v>
+        <v>835</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>630</v>
@@ -28820,21 +27780,21 @@
         <v>96256</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>822</v>
+        <v>836</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>824</v>
+        <v>838</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>825</v>
+        <v>839</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>194</v>
@@ -28864,12 +27824,12 @@
         <v>60113.52</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>826</v>
+        <v>840</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>367</v>
@@ -28908,12 +27868,12 @@
         <v>27351</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>827</v>
+        <v>841</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>823</v>
+        <v>837</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>537</v>
@@ -30453,7 +29413,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>511</v>
@@ -30492,12 +29452,12 @@
         <v>0</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>828</v>
+        <v>842</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>817</v>
+        <v>831</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>511</v>
@@ -30536,7 +29496,7 @@
         <v>21440</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30562,7 +29522,7 @@
       </c>
       <c r="J60" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K60" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -30570,7 +29530,7 @@
       </c>
       <c r="L60" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30604,7 +29564,7 @@
       </c>
       <c r="L62" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30613,7 +29573,7 @@
       </c>
       <c r="J63" s="8" t="n">
         <f aca="false">J59*(1+J60)*(1+J61)*J62</f>
-        <v>278660.2853727</v>
+        <v>282782.0678886</v>
       </c>
       <c r="K63" s="8" t="n">
         <f aca="false">K59*(1+K60)*(1+K61)*K62</f>
@@ -30621,7 +29581,7 @@
       </c>
       <c r="L63" s="8" t="n">
         <f aca="false">L59*(1+L60)*(1+L61)*L62</f>
-        <v>651156.78925</v>
+        <v>578321.9425688</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30661,7 +29621,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>830</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30706,7 +29666,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>831</v>
+        <v>845</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30738,17 +29698,17 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>832</v>
+        <v>846</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>833</v>
+        <v>847</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>834</v>
+        <v>848</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30758,7 +29718,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
-        <v>835</v>
+        <v>849</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30931,7 +29891,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>836</v>
+        <v>850</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31728,16 +30688,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>838</v>
+        <v>852</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>317</v>
@@ -31767,21 +30727,21 @@
         <v>7200</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>840</v>
+        <v>854</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>841</v>
+        <v>855</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>192</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>842</v>
+        <v>856</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>194</v>
@@ -31811,21 +30771,21 @@
         <v>21840</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>843</v>
+        <v>857</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>844</v>
+        <v>858</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>845</v>
+        <v>859</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>194</v>
@@ -31855,21 +30815,21 @@
         <v>4944</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>846</v>
+        <v>860</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>317</v>
@@ -31899,21 +30859,21 @@
         <v>21213.12</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>838</v>
+        <v>852</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>839</v>
+        <v>853</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>317</v>
@@ -31943,21 +30903,21 @@
         <v>14400</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>851</v>
+        <v>865</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>853</v>
+        <v>867</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>194</v>
@@ -31987,21 +30947,21 @@
         <v>141056</v>
       </c>
       <c r="M45" s="5" t="s">
-        <v>854</v>
+        <v>868</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>855</v>
+        <v>869</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>856</v>
+        <v>870</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>277</v>
@@ -32031,21 +30991,21 @@
         <v>33100.2</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>857</v>
+        <v>871</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>847</v>
+        <v>861</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>317</v>
@@ -32075,21 +31035,21 @@
         <v>42426.24</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>859</v>
+        <v>873</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>860</v>
+        <v>874</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>277</v>
@@ -32119,21 +31079,21 @@
         <v>13380.94</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>861</v>
+        <v>875</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>858</v>
+        <v>872</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>863</v>
+        <v>877</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>277</v>
@@ -32163,7 +31123,7 @@
         <v>6936.34</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>864</v>
+        <v>878</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32207,7 +31167,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>865</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32629,7 +31589,7 @@
       </c>
       <c r="J61" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K61" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -32637,7 +31597,7 @@
       </c>
       <c r="L61" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32671,7 +31631,7 @@
       </c>
       <c r="L63" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32680,7 +31640,7 @@
       </c>
       <c r="J64" s="8" t="n">
         <f aca="false">J60*(1+J61)*(1+J62)*J63</f>
-        <v>1348883.22675834</v>
+        <v>1364334.48111168</v>
       </c>
       <c r="K64" s="8" t="n">
         <f aca="false">K60*(1+K61)*(1+K62)*K63</f>
@@ -32688,7 +31648,7 @@
       </c>
       <c r="L64" s="8" t="n">
         <f aca="false">L60*(1+L61)*(1+L62)*L63</f>
-        <v>7453266.74352753</v>
+        <v>6597891.57914224</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32728,7 +31688,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>866</v>
+        <v>880</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32773,7 +31733,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>867</v>
+        <v>881</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32805,22 +31765,22 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>868</v>
+        <v>882</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>869</v>
+        <v>883</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>870</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>871</v>
+        <v>885</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33371,7 +32331,7 @@
       </c>
       <c r="J30" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K30" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -33379,7 +32339,7 @@
       </c>
       <c r="L30" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33413,7 +32373,7 @@
       </c>
       <c r="L32" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33422,7 +32382,7 @@
       </c>
       <c r="J33" s="8" t="n">
         <f aca="false">J29*(1+J30)*(1+J31)*J32</f>
-        <v>584464.7078424</v>
+        <v>593109.7733232</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">K29*(1+K30)*(1+K31)*K32</f>
@@ -33430,7 +32390,7 @@
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">L29*(1+L30)*(1+L31)*L32</f>
-        <v>4943798.2385</v>
+        <v>4390811.9337136</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33454,7 +32414,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -33470,7 +32430,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>872</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33507,7 +32467,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33515,7 +32475,7 @@
         <v>160</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>873</v>
+        <v>887</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33523,7 +32483,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33547,22 +32507,22 @@
         <v>166</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>874</v>
+        <v>888</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="20" t="s">
-        <v>875</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="20" t="s">
-        <v>556</v>
+        <v>890</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="20" t="s">
-        <v>876</v>
+        <v>891</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33647,1504 +32607,316 @@
         <v>2729.82</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>218</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>557</v>
+        <v>333</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>220</v>
+        <v>502</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>221</v>
+        <v>503</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>188</v>
       </c>
       <c r="F19" s="21" t="n">
-        <v>4.43</v>
+        <v>0.76</v>
       </c>
       <c r="G19" s="21" t="n">
-        <v>50</v>
+        <v>4500</v>
       </c>
       <c r="H19" s="21" t="n">
-        <v>187.5</v>
+        <v>7500</v>
       </c>
       <c r="I19" s="21" t="n">
-        <v>562.5</v>
+        <v>10500</v>
       </c>
       <c r="J19" s="22" t="n">
         <f aca="false">F19*G19</f>
-        <v>221.5</v>
+        <v>3420</v>
       </c>
       <c r="K19" s="22" t="n">
         <f aca="false">F19*H19</f>
-        <v>830.625</v>
+        <v>5700</v>
       </c>
       <c r="L19" s="22" t="n">
         <f aca="false">F19*I19</f>
-        <v>2491.875</v>
+        <v>7980</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>222</v>
+        <v>892</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>557</v>
+        <v>893</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>223</v>
+        <v>838</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>224</v>
+        <v>839</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F20" s="21" t="n">
-        <v>9.56</v>
+        <v>172.74</v>
       </c>
       <c r="G20" s="21" t="n">
-        <v>25</v>
+        <v>1500</v>
       </c>
       <c r="H20" s="21" t="n">
-        <v>93.75</v>
+        <v>2500</v>
       </c>
       <c r="I20" s="21" t="n">
-        <v>281.25</v>
+        <v>3500</v>
       </c>
       <c r="J20" s="22" t="n">
         <f aca="false">F20*G20</f>
-        <v>239</v>
+        <v>259110</v>
       </c>
       <c r="K20" s="22" t="n">
         <f aca="false">F20*H20</f>
-        <v>896.25</v>
+        <v>431850</v>
       </c>
       <c r="L20" s="22" t="n">
         <f aca="false">F20*I20</f>
-        <v>2688.75</v>
+        <v>604590</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>225</v>
+        <v>894</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>557</v>
+        <v>893</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>226</v>
+        <v>895</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>227</v>
+        <v>896</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F21" s="21" t="n">
-        <v>2.58</v>
+        <v>34.89</v>
       </c>
       <c r="G21" s="21" t="n">
-        <v>40</v>
+        <v>1500</v>
       </c>
       <c r="H21" s="21" t="n">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="I21" s="21" t="n">
-        <v>450</v>
+        <v>3500</v>
       </c>
       <c r="J21" s="22" t="n">
         <f aca="false">F21*G21</f>
-        <v>103.2</v>
+        <v>52335</v>
       </c>
       <c r="K21" s="22" t="n">
         <f aca="false">F21*H21</f>
-        <v>387</v>
+        <v>87225</v>
       </c>
       <c r="L21" s="22" t="n">
         <f aca="false">F21*I21</f>
-        <v>1161</v>
+        <v>122115</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>228</v>
+        <v>897</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>557</v>
+        <v>898</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>229</v>
+        <v>478</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>230</v>
+        <v>479</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>188</v>
       </c>
       <c r="F22" s="21" t="n">
-        <v>10.04</v>
+        <v>581.71</v>
       </c>
       <c r="G22" s="21" t="n">
-        <v>20</v>
+        <v>8.8</v>
       </c>
       <c r="H22" s="21" t="n">
-        <v>90</v>
+        <v>17.6</v>
       </c>
       <c r="I22" s="21" t="n">
-        <v>270</v>
+        <v>26.4</v>
       </c>
       <c r="J22" s="22" t="n">
         <f aca="false">F22*G22</f>
-        <v>200.8</v>
+        <v>5119.048</v>
       </c>
       <c r="K22" s="22" t="n">
         <f aca="false">F22*H22</f>
-        <v>903.6</v>
+        <v>10238.096</v>
       </c>
       <c r="L22" s="22" t="n">
         <f aca="false">F22*I22</f>
-        <v>2710.8</v>
+        <v>15357.144</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>231</v>
+        <v>899</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>557</v>
+        <v>900</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>232</v>
+        <v>901</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>233</v>
+        <v>902</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>188</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>28.42</v>
+        <v>882.89</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>81</v>
+        <v>17.5</v>
       </c>
       <c r="J23" s="22" t="n">
         <f aca="false">F23*G23</f>
-        <v>170.52</v>
+        <v>6621.675</v>
       </c>
       <c r="K23" s="22" t="n">
         <f aca="false">F23*H23</f>
-        <v>767.34</v>
+        <v>11036.125</v>
       </c>
       <c r="L23" s="22" t="n">
         <f aca="false">F23*I23</f>
-        <v>2302.02</v>
+        <v>15450.575</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>234</v>
+        <v>903</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>30.78</v>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I24" s="21" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J24" s="22" t="n">
-        <f aca="false">F24*G24</f>
-        <v>92.34</v>
-      </c>
-      <c r="K24" s="22" t="n">
-        <f aca="false">F24*H24</f>
-        <v>415.53</v>
-      </c>
-      <c r="L24" s="22" t="n">
-        <f aca="false">F24*I24</f>
-        <v>1246.59</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>237</v>
+      <c r="I24" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="J24" s="23" t="n">
+        <f aca="false">SUM(J18:J23)</f>
+        <v>329335.543</v>
+      </c>
+      <c r="K24" s="23" t="n">
+        <f aca="false">SUM(K18:K23)</f>
+        <v>548779.041</v>
+      </c>
+      <c r="L24" s="23" t="n">
+        <f aca="false">SUM(L18:L23)</f>
+        <v>768222.539</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>101.54</v>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="H25" s="21" t="n">
-        <v>93.75</v>
-      </c>
-      <c r="I25" s="21" t="n">
-        <v>281.25</v>
-      </c>
-      <c r="J25" s="22" t="n">
-        <f aca="false">F25*G25</f>
-        <v>2538.5</v>
-      </c>
-      <c r="K25" s="22" t="n">
-        <f aca="false">F25*H25</f>
-        <v>9519.375</v>
-      </c>
-      <c r="L25" s="22" t="n">
-        <f aca="false">F25*I25</f>
-        <v>28558.125</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>50</v>
-      </c>
-      <c r="H26" s="21" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="I26" s="21" t="n">
-        <v>562.5</v>
-      </c>
-      <c r="J26" s="22" t="n">
-        <f aca="false">F26*G26</f>
-        <v>2121</v>
-      </c>
-      <c r="K26" s="22" t="n">
-        <f aca="false">F26*H26</f>
-        <v>7953.75</v>
-      </c>
-      <c r="L26" s="22" t="n">
-        <f aca="false">F26*I26</f>
-        <v>23861.25</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="G27" s="21" t="n">
-        <v>40</v>
-      </c>
-      <c r="H27" s="21" t="n">
-        <v>150</v>
-      </c>
-      <c r="I27" s="21" t="n">
-        <v>450</v>
-      </c>
-      <c r="J27" s="22" t="n">
-        <f aca="false">F27*G27</f>
-        <v>2928</v>
-      </c>
-      <c r="K27" s="22" t="n">
-        <f aca="false">F27*H27</f>
-        <v>10980</v>
-      </c>
-      <c r="L27" s="22" t="n">
-        <f aca="false">F27*I27</f>
-        <v>32940</v>
-      </c>
-      <c r="M27" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="H28" s="21" t="n">
-        <v>216</v>
-      </c>
-      <c r="I28" s="21" t="n">
-        <v>648</v>
-      </c>
-      <c r="J28" s="22" t="n">
-        <f aca="false">F28*G28</f>
-        <v>289.44</v>
-      </c>
-      <c r="K28" s="22" t="n">
-        <f aca="false">F28*H28</f>
-        <v>1302.48</v>
-      </c>
-      <c r="L28" s="22" t="n">
-        <f aca="false">F28*I28</f>
-        <v>3907.44</v>
-      </c>
-      <c r="M28" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F29" s="21" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="G29" s="21" t="n">
-        <v>48</v>
-      </c>
-      <c r="H29" s="21" t="n">
-        <v>216</v>
-      </c>
-      <c r="I29" s="21" t="n">
-        <v>648</v>
-      </c>
-      <c r="J29" s="22" t="n">
-        <f aca="false">F29*G29</f>
-        <v>1525.92</v>
-      </c>
-      <c r="K29" s="22" t="n">
-        <f aca="false">F29*H29</f>
-        <v>6866.64</v>
-      </c>
-      <c r="L29" s="22" t="n">
-        <f aca="false">F29*I29</f>
-        <v>20599.92</v>
-      </c>
-      <c r="M29" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F30" s="21" t="n">
-        <v>59.3</v>
-      </c>
-      <c r="G30" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="H30" s="21" t="n">
-        <v>27</v>
-      </c>
-      <c r="I30" s="21" t="n">
-        <v>81</v>
-      </c>
-      <c r="J30" s="22" t="n">
-        <f aca="false">F30*G30</f>
-        <v>355.8</v>
-      </c>
-      <c r="K30" s="22" t="n">
-        <f aca="false">F30*H30</f>
-        <v>1601.1</v>
-      </c>
-      <c r="L30" s="22" t="n">
-        <f aca="false">F30*I30</f>
-        <v>4803.3</v>
-      </c>
-      <c r="M30" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F31" s="21" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="G31" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I31" s="21" t="n">
-        <v>270</v>
-      </c>
-      <c r="J31" s="22" t="n">
-        <f aca="false">F31*G31</f>
-        <v>1163.8</v>
-      </c>
-      <c r="K31" s="22" t="n">
-        <f aca="false">F31*H31</f>
-        <v>5237.1</v>
-      </c>
-      <c r="L31" s="22" t="n">
-        <f aca="false">F31*I31</f>
-        <v>15711.3</v>
-      </c>
-      <c r="M31" s="5" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="s">
-        <v>559</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>50.14</v>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>20</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>270</v>
-      </c>
-      <c r="J32" s="22" t="n">
-        <f aca="false">F32*G32</f>
-        <v>1002.8</v>
-      </c>
-      <c r="K32" s="22" t="n">
-        <f aca="false">F32*H32</f>
-        <v>4512.6</v>
-      </c>
-      <c r="L32" s="22" t="n">
-        <f aca="false">F32*I32</f>
-        <v>13537.8</v>
-      </c>
-      <c r="M32" s="5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="G33" s="21" t="n">
-        <v>600</v>
-      </c>
-      <c r="H33" s="21" t="n">
-        <v>900</v>
-      </c>
-      <c r="I33" s="21" t="n">
-        <v>1350</v>
-      </c>
-      <c r="J33" s="22" t="n">
-        <f aca="false">F33*G33</f>
-        <v>7398</v>
-      </c>
-      <c r="K33" s="22" t="n">
-        <f aca="false">F33*H33</f>
-        <v>11097</v>
-      </c>
-      <c r="L33" s="22" t="n">
-        <f aca="false">F33*I33</f>
-        <v>16645.5</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>15.25</v>
-      </c>
-      <c r="G34" s="21" t="n">
-        <v>60</v>
-      </c>
-      <c r="H34" s="21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I34" s="21" t="n">
-        <v>135</v>
-      </c>
-      <c r="J34" s="22" t="n">
-        <f aca="false">F34*G34</f>
-        <v>915</v>
-      </c>
-      <c r="K34" s="22" t="n">
-        <f aca="false">F34*H34</f>
-        <v>1372.5</v>
-      </c>
-      <c r="L34" s="22" t="n">
-        <f aca="false">F34*I34</f>
-        <v>2058.75</v>
-      </c>
-      <c r="M34" s="5" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <v>223.25</v>
-      </c>
-      <c r="G35" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="H35" s="21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="I35" s="21" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="J35" s="22" t="n">
-        <f aca="false">F35*G35</f>
-        <v>669.75</v>
-      </c>
-      <c r="K35" s="22" t="n">
-        <f aca="false">F35*H35</f>
-        <v>3013.875</v>
-      </c>
-      <c r="L35" s="22" t="n">
-        <f aca="false">F35*I35</f>
-        <v>9041.625</v>
-      </c>
-      <c r="M35" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F36" s="21" t="n">
-        <v>1179.17</v>
-      </c>
-      <c r="G36" s="21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H36" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I36" s="21" t="n">
-        <v>18</v>
-      </c>
-      <c r="J36" s="22" t="n">
-        <f aca="false">F36*G36</f>
-        <v>1568.2961</v>
-      </c>
-      <c r="K36" s="22" t="n">
-        <f aca="false">F36*H36</f>
-        <v>7075.02</v>
-      </c>
-      <c r="L36" s="22" t="n">
-        <f aca="false">F36*I36</f>
-        <v>21225.06</v>
-      </c>
-      <c r="M36" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F37" s="21" t="n">
-        <v>53.69</v>
-      </c>
-      <c r="G37" s="21" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H37" s="21" t="n">
-        <v>25</v>
-      </c>
-      <c r="I37" s="21" t="n">
-        <v>75</v>
-      </c>
-      <c r="J37" s="22" t="n">
-        <f aca="false">F37*G37</f>
-        <v>358.1123</v>
-      </c>
-      <c r="K37" s="22" t="n">
-        <f aca="false">F37*H37</f>
-        <v>1342.25</v>
-      </c>
-      <c r="L37" s="22" t="n">
-        <f aca="false">F37*I37</f>
-        <v>4026.75</v>
-      </c>
-      <c r="M37" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F38" s="21" t="n">
-        <v>30.86</v>
-      </c>
-      <c r="G38" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="H38" s="21" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="I38" s="21" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="J38" s="22" t="n">
-        <f aca="false">F38*G38</f>
-        <v>154.3</v>
-      </c>
-      <c r="K38" s="22" t="n">
-        <f aca="false">F38*H38</f>
-        <v>578.625</v>
-      </c>
-      <c r="L38" s="22" t="n">
-        <f aca="false">F38*I38</f>
-        <v>1735.875</v>
-      </c>
-      <c r="M38" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F39" s="21" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="G39" s="21" t="n">
-        <v>480</v>
-      </c>
-      <c r="H39" s="21" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I39" s="21" t="n">
-        <v>5400</v>
-      </c>
-      <c r="J39" s="22" t="n">
-        <f aca="false">F39*G39</f>
-        <v>2630.4</v>
-      </c>
-      <c r="K39" s="22" t="n">
-        <f aca="false">F39*H39</f>
-        <v>9864</v>
-      </c>
-      <c r="L39" s="22" t="n">
-        <f aca="false">F39*I39</f>
-        <v>29592</v>
-      </c>
-      <c r="M39" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F40" s="21" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="G40" s="21" t="n">
-        <v>160</v>
-      </c>
-      <c r="H40" s="21" t="n">
-        <v>600</v>
-      </c>
-      <c r="I40" s="21" t="n">
-        <v>1800</v>
-      </c>
-      <c r="J40" s="22" t="n">
-        <f aca="false">F40*G40</f>
-        <v>1792</v>
-      </c>
-      <c r="K40" s="22" t="n">
-        <f aca="false">F40*H40</f>
-        <v>6720</v>
-      </c>
-      <c r="L40" s="22" t="n">
-        <f aca="false">F40*I40</f>
-        <v>20160</v>
-      </c>
-      <c r="M40" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F41" s="21" t="n">
-        <v>623.29</v>
-      </c>
-      <c r="G41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" s="22" t="n">
-        <f aca="false">F41*G41</f>
-        <v>623.29</v>
-      </c>
-      <c r="K41" s="22" t="n">
-        <f aca="false">F41*H41</f>
-        <v>623.29</v>
-      </c>
-      <c r="L41" s="22" t="n">
-        <f aca="false">F41*I41</f>
-        <v>1869.87</v>
-      </c>
-      <c r="M41" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F42" s="21" t="n">
-        <v>630.3</v>
-      </c>
-      <c r="G42" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" s="21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I42" s="21" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J42" s="22" t="n">
-        <f aca="false">F42*G42</f>
-        <v>630.3</v>
-      </c>
-      <c r="K42" s="22" t="n">
-        <f aca="false">F42*H42</f>
-        <v>2363.625</v>
-      </c>
-      <c r="L42" s="22" t="n">
-        <f aca="false">F42*I42</f>
-        <v>7090.875</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F43" s="21" t="n">
-        <v>368.02</v>
-      </c>
-      <c r="G43" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="I43" s="21" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J43" s="22" t="n">
-        <f aca="false">F43*G43</f>
-        <v>368.02</v>
-      </c>
-      <c r="K43" s="22" t="n">
-        <f aca="false">F43*H43</f>
-        <v>1380.075</v>
-      </c>
-      <c r="L43" s="22" t="n">
-        <f aca="false">F43*I43</f>
-        <v>4140.225</v>
-      </c>
-      <c r="M43" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
-        <v>561</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F44" s="21" t="n">
-        <v>43.26</v>
-      </c>
-      <c r="G44" s="21" t="n">
-        <v>12</v>
-      </c>
-      <c r="H44" s="21" t="n">
-        <v>45</v>
-      </c>
-      <c r="I44" s="21" t="n">
-        <v>135</v>
-      </c>
-      <c r="J44" s="22" t="n">
-        <f aca="false">F44*G44</f>
-        <v>519.12</v>
-      </c>
-      <c r="K44" s="22" t="n">
-        <f aca="false">F44*H44</f>
-        <v>1946.7</v>
-      </c>
-      <c r="L44" s="22" t="n">
-        <f aca="false">F44*I44</f>
-        <v>5840.1</v>
-      </c>
-      <c r="M44" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F45" s="21" t="n">
-        <v>288.1</v>
-      </c>
-      <c r="G45" s="21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="H45" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="I45" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="22" t="n">
-        <f aca="false">F45*G45</f>
-        <v>383.173</v>
-      </c>
-      <c r="K45" s="22" t="n">
-        <f aca="false">F45*H45</f>
-        <v>576.2</v>
-      </c>
-      <c r="L45" s="22" t="n">
-        <f aca="false">F45*I45</f>
-        <v>864.3</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F46" s="21" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="G46" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I46" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="J46" s="22" t="n">
-        <f aca="false">F46*G46</f>
-        <v>71.84</v>
-      </c>
-      <c r="K46" s="22" t="n">
-        <f aca="false">F46*H46</f>
-        <v>107.76</v>
-      </c>
-      <c r="L46" s="22" t="n">
-        <f aca="false">F46*I46</f>
-        <v>161.64</v>
-      </c>
-      <c r="M46" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="G47" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="I47" s="21" t="n">
-        <v>9</v>
-      </c>
-      <c r="J47" s="22" t="n">
-        <f aca="false">F47*G47</f>
-        <v>81.88</v>
-      </c>
-      <c r="K47" s="22" t="n">
-        <f aca="false">F47*H47</f>
-        <v>122.82</v>
-      </c>
-      <c r="L47" s="22" t="n">
-        <f aca="false">F47*I47</f>
-        <v>184.23</v>
-      </c>
-      <c r="M47" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="F48" s="21" t="n">
-        <v>9.88</v>
-      </c>
-      <c r="G48" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="H48" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="I48" s="21" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="J48" s="22" t="n">
-        <f aca="false">F48*G48</f>
-        <v>98.8</v>
-      </c>
-      <c r="K48" s="22" t="n">
-        <f aca="false">F48*H48</f>
-        <v>148.2</v>
-      </c>
-      <c r="L48" s="22" t="n">
-        <f aca="false">F48*I48</f>
-        <v>222.3</v>
-      </c>
-      <c r="M48" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F49" s="21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="G49" s="21" t="n">
-        <v>100</v>
-      </c>
-      <c r="H49" s="21" t="n">
-        <v>150</v>
-      </c>
-      <c r="I49" s="21" t="n">
-        <v>225</v>
-      </c>
-      <c r="J49" s="22" t="n">
-        <f aca="false">F49*G49</f>
-        <v>283</v>
-      </c>
-      <c r="K49" s="22" t="n">
-        <f aca="false">F49*H49</f>
-        <v>424.5</v>
-      </c>
-      <c r="L49" s="22" t="n">
-        <f aca="false">F49*I49</f>
-        <v>636.75</v>
-      </c>
-      <c r="M49" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>562</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>877</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>878</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="F50" s="21" t="n">
-        <v>1253.09</v>
-      </c>
-      <c r="G50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="J50" s="22" t="n">
-        <f aca="false">F50*G50</f>
-        <v>1253.09</v>
-      </c>
-      <c r="K50" s="22" t="n">
-        <f aca="false">F50*H50</f>
-        <v>1253.09</v>
-      </c>
-      <c r="L50" s="22" t="n">
-        <f aca="false">F50*I50</f>
-        <v>2506.18</v>
-      </c>
-      <c r="M50" s="5" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I51" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="J51" s="23" t="n">
-        <f aca="false">SUM(J18:J50)</f>
-        <v>35480.8114</v>
-      </c>
-      <c r="K51" s="23" t="n">
-        <f aca="false">SUM(K18:K50)</f>
-        <v>104912.74</v>
-      </c>
-      <c r="L51" s="23" t="n">
-        <f aca="false">SUM(L18:L50)</f>
-        <v>287252.02</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I52" s="7" t="s">
+      <c r="I25" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="J52" s="24" t="n">
+      <c r="J25" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
-      </c>
-      <c r="K52" s="24" t="n">
+        <v>0.2212</v>
+      </c>
+      <c r="K25" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
         <v>0.2212</v>
       </c>
-      <c r="L52" s="24" t="n">
+      <c r="L25" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I53" s="7" t="s">
+        <v>0.2212</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I26" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="J53" s="24" t="n">
+      <c r="J26" s="24" t="n">
         <f aca="false">PARAMETROS!$B$8</f>
         <v>0.05</v>
       </c>
-      <c r="K53" s="24" t="n">
+      <c r="K26" s="24" t="n">
         <f aca="false">PARAMETROS!$C$8</f>
         <v>0.1</v>
       </c>
-      <c r="L53" s="24" t="n">
+      <c r="L26" s="24" t="n">
         <f aca="false">PARAMETROS!$D$8</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I54" s="7" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I27" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="J54" s="25" t="n">
+      <c r="J27" s="25" t="n">
         <f aca="false">PARAMETROS!$B$9</f>
         <v>1</v>
       </c>
-      <c r="K54" s="25" t="n">
+      <c r="K27" s="25" t="n">
         <f aca="false">PARAMETROS!$C$9</f>
         <v>1</v>
       </c>
-      <c r="L54" s="25" t="n">
+      <c r="L27" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I55" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="J55" s="8" t="n">
-        <f aca="false">J51*(1+J52)*(1+J53)*J54</f>
-        <v>44832.488860698</v>
-      </c>
-      <c r="K55" s="8" t="n">
-        <f aca="false">K51*(1+K52)*(1+K53)*K54</f>
-        <v>140931.3818968</v>
-      </c>
-      <c r="L55" s="8" t="n">
-        <f aca="false">L51*(1+L52)*(1+L53)*L54</f>
-        <v>454217.256625</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="26" t="s">
+      <c r="J28" s="8" t="n">
+        <f aca="false">J24*(1+J25)*(1+J26)*J27</f>
+        <v>422293.79336718</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <f aca="false">K24*(1+K25)*(1+K26)*K27</f>
+        <v>737185.86135612</v>
+      </c>
+      <c r="L28" s="8" t="n">
+        <f aca="false">L24*(1+L25)*(1+L26)*L27</f>
+        <v>1078876.36932082</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
         <v>327</v>
       </c>
     </row>
@@ -35174,7 +32946,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35184,178 +32956,178 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="C5" s="27" t="s">
-        <v>886</v>
+        <v>910</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>887</v>
+        <v>911</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>894</v>
+        <v>918</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>895</v>
+        <v>919</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>896</v>
+        <v>920</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>897</v>
+        <v>921</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>898</v>
+        <v>922</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>899</v>
+        <v>923</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>901</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>902</v>
+        <v>926</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>903</v>
+        <v>927</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>904</v>
+        <v>928</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>905</v>
+        <v>929</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
-        <v>906</v>
+        <v>930</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="C13" s="27" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>909</v>
+        <v>933</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="C15" s="27" t="s">
-        <v>912</v>
+        <v>936</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
-        <v>913</v>
+        <v>937</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="C16" s="27" t="s">
-        <v>914</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
-        <v>915</v>
+        <v>939</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="C17" s="27" t="s">
-        <v>917</v>
+        <v>941</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>918</v>
+        <v>942</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
-        <v>920</v>
+        <v>944</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>897</v>
+        <v>945</v>
       </c>
       <c r="C19" s="27" t="s">
-        <v>921</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -35374,7 +33146,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="160"/>
@@ -35382,7 +33154,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>922</v>
+        <v>947</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35392,47 +33164,52 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
-        <v>923</v>
+        <v>948</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
-        <v>924</v>
+        <v>949</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
-        <v>925</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
-        <v>926</v>
+        <v>951</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
-        <v>927</v>
+        <v>952</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
-        <v>930</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
-        <v>931</v>
+        <v>956</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="27" t="s">
+        <v>957</v>
       </c>
     </row>
   </sheetData>
@@ -37386,7 +35163,7 @@
       </c>
       <c r="J59" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K59" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -37394,7 +35171,7 @@
       </c>
       <c r="L59" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37428,7 +35205,7 @@
       </c>
       <c r="L61" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37437,7 +35214,7 @@
       </c>
       <c r="J62" s="8" t="n">
         <f aca="false">J58*(1+J59)*(1+J60)*J61</f>
-        <v>20375.386944066</v>
+        <v>20676.767937588</v>
       </c>
       <c r="K62" s="8" t="n">
         <f aca="false">K58*(1+K59)*(1+K60)*K61</f>
@@ -37445,7 +35222,7 @@
       </c>
       <c r="L62" s="8" t="n">
         <f aca="false">L58*(1+L59)*(1+L60)*L61</f>
-        <v>554590.51998625</v>
+        <v>492557.049459788</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39135,7 +36912,7 @@
       </c>
       <c r="J52" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K52" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -39143,7 +36920,7 @@
       </c>
       <c r="L52" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39177,7 +36954,7 @@
       </c>
       <c r="L54" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39186,7 +36963,7 @@
       </c>
       <c r="J55" s="8" t="n">
         <f aca="false">J51*(1+J52)*(1+J53)*J54</f>
-        <v>330852.0063156</v>
+        <v>335745.7787208</v>
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">K51*(1+K52)*(1+K53)*K54</f>
@@ -39194,7 +36971,7 @@
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">L51*(1+L52)*(1+L53)*L54</f>
-        <v>1609322.696575</v>
+        <v>1429312.63785992</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40268,7 +38045,7 @@
       </c>
       <c r="J38" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K38" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -40276,7 +38053,7 @@
       </c>
       <c r="L38" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40310,7 +38087,7 @@
       </c>
       <c r="L40" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40319,7 +38096,7 @@
       </c>
       <c r="J41" s="8" t="n">
         <f aca="false">J37*(1+J38)*(1+J39)*J40</f>
-        <v>2199510.94038312</v>
+        <v>2224706.00717513</v>
       </c>
       <c r="K41" s="8" t="n">
         <f aca="false">K37*(1+K38)*(1+K39)*K40</f>
@@ -40327,7 +38104,7 @@
       </c>
       <c r="L41" s="8" t="n">
         <f aca="false">L37*(1+L38)*(1+L39)*L40</f>
-        <v>4174865.17984169</v>
+        <v>3695736.21366124</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41308,7 +39085,7 @@
       </c>
       <c r="J35" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K35" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -41316,7 +39093,7 @@
       </c>
       <c r="L35" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41350,7 +39127,7 @@
       </c>
       <c r="L37" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41359,7 +39136,7 @@
       </c>
       <c r="J38" s="8" t="n">
         <f aca="false">J34*(1+J35)*(1+J36)*J37</f>
-        <v>8137.2391716</v>
+        <v>8257.6005288</v>
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">K34*(1+K35)*(1+K36)*K37</f>
@@ -41367,7 +39144,7 @@
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">L34*(1+L35)*(1+L36)*L37</f>
-        <v>16216.155965625</v>
+        <v>14402.30521107</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42353,7 +40130,7 @@
       </c>
       <c r="J36" s="24" t="n">
         <f aca="false">PARAMETROS!$B$7</f>
-        <v>0.196</v>
+        <v>0.2097</v>
       </c>
       <c r="K36" s="24" t="n">
         <f aca="false">PARAMETROS!$C$7</f>
@@ -42361,7 +40138,7 @@
       </c>
       <c r="L36" s="24" t="n">
         <f aca="false">PARAMETROS!$D$7</f>
-        <v>0.2423</v>
+        <v>0.2097</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42395,7 +40172,7 @@
       </c>
       <c r="L38" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42404,7 +40181,7 @@
       </c>
       <c r="J39" s="8" t="n">
         <f aca="false">J35*(1+J36)*(1+J37)*J38</f>
-        <v>63307.48679892</v>
+        <v>64032.664532319</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">K35*(1+K36)*(1+K37)*K38</f>
@@ -42412,7 +40189,7 @@
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">L35*(1+L36)*(1+L37)*L38</f>
-        <v>351155.122714659</v>
+        <v>310854.75763278</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44850,7 +42627,7 @@
       </c>
       <c r="J69" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K69" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -44858,7 +42635,7 @@
       </c>
       <c r="L69" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44892,7 +42669,7 @@
       </c>
       <c r="L71" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44901,7 +42678,7 @@
       </c>
       <c r="J72" s="8" t="n">
         <f aca="false">J68*(1+J69)*(1+J70)*J71</f>
-        <v>638222.7754287</v>
+        <v>647662.9992966</v>
       </c>
       <c r="K72" s="8" t="n">
         <f aca="false">K68*(1+K69)*(1+K70)*K71</f>
@@ -44909,7 +42686,7 @@
       </c>
       <c r="L72" s="8" t="n">
         <f aca="false">L68*(1+L69)*(1+L70)*L71</f>
-        <v>1166732.33325</v>
+        <v>1036228.0184472</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46511,7 +44288,7 @@
       </c>
       <c r="J50" s="24" t="n">
         <f aca="false">PARAMETROS!$B$6</f>
-        <v>0.2034</v>
+        <v>0.2212</v>
       </c>
       <c r="K50" s="24" t="n">
         <f aca="false">PARAMETROS!$C$6</f>
@@ -46519,7 +44296,7 @@
       </c>
       <c r="L50" s="24" t="n">
         <f aca="false">PARAMETROS!$D$6</f>
-        <v>0.25</v>
+        <v>0.2212</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46553,7 +44330,7 @@
       </c>
       <c r="L52" s="25" t="n">
         <f aca="false">PARAMETROS!$D$9</f>
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46562,7 +44339,7 @@
       </c>
       <c r="J53" s="8" t="n">
         <f aca="false">J49*(1+J50)*(1+J51)*J52</f>
-        <v>297660.85913025</v>
+        <v>302063.6871945</v>
       </c>
       <c r="K53" s="8" t="n">
         <f aca="false">K49*(1+K50)*(1+K51)*K52</f>
@@ -46570,7 +44347,7 @@
       </c>
       <c r="L53" s="8" t="n">
         <f aca="false">L49*(1+L50)*(1+L51)*L52</f>
-        <v>2481754.0125675</v>
+        <v>2204158.54556177</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
